--- a/ia_hybride/evaluation/comparaison_hybride_vs_llm.xlsx
+++ b/ia_hybride/evaluation/comparaison_hybride_vs_llm.xlsx
@@ -72,12 +72,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
+        <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
+        <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
   </fills>
@@ -127,19 +127,19 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="164" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -507,13 +507,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -526,7 +527,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Modèle : qwen3:8b — généré le 2026-06-15 10:46 UTC</t>
+          <t>Modèle : qwen3:8b — généré le 2026-07-02 12:07 UTC</t>
         </is>
       </c>
     </row>
@@ -538,17 +539,22 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Hybride</t>
+          <t>Hybride (LLM+ODM)</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>LLM rapide (no_think, T=0)</t>
+          <t>LLM T=0 (no_think)</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>LLM raisonnement (T=0.2)</t>
+          <t>LLM T=0.2 (no_think)</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>LLM T=0.2 + raisonnement</t>
         </is>
       </c>
     </row>
@@ -559,13 +565,16 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>52</v>
+        <v>78</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>78</v>
       </c>
     </row>
     <row r="6">
@@ -575,13 +584,16 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>52</v>
+        <v>77</v>
       </c>
       <c r="C6" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="D6" s="5" t="n">
         <v>27</v>
       </c>
-      <c r="D6" s="5" t="n">
-        <v>30</v>
+      <c r="E6" s="5" t="n">
+        <v>41</v>
       </c>
     </row>
     <row r="7">
@@ -591,13 +603,16 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>22</v>
+        <v>51</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>37</v>
       </c>
     </row>
     <row r="8">
@@ -607,13 +622,16 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>1</v>
+        <v>0.9871794871794872</v>
       </c>
       <c r="C8" s="6" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.358974358974359</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>0.5769230769230769</v>
+        <v>0.3461538461538461</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>0.5256410256410257</v>
       </c>
     </row>
     <row r="9">
@@ -623,13 +641,16 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>0</v>
+        <v>0.01282051282051277</v>
       </c>
       <c r="C9" s="6" t="n">
-        <v>0.4807692307692307</v>
+        <v>0.641025641025641</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>0.4230769230769231</v>
+        <v>0.6538461538461539</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>0.4743589743589743</v>
       </c>
     </row>
   </sheetData>
@@ -643,14 +664,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
     <col width="6" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -678,12 +700,17 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>LLM rapide %</t>
+          <t>LLM T=0 %</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>LLM raisonn. %</t>
+          <t>LLM T=0.2 %</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>LLM T=0.2+rais. %</t>
         </is>
       </c>
     </row>
@@ -694,16 +721,19 @@
         </is>
       </c>
       <c r="B4" s="8" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C4" s="9" t="n">
         <v>1</v>
       </c>
       <c r="D4" s="10" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="E4" s="10" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.25</v>
+      </c>
+      <c r="F4" s="11" t="n">
+        <v>0.5</v>
       </c>
     </row>
     <row r="5">
@@ -713,16 +743,19 @@
         </is>
       </c>
       <c r="B5" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C5" s="9" t="n">
         <v>1</v>
       </c>
       <c r="D5" s="10" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="E5" s="11" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
+      </c>
+      <c r="E5" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="11" t="n">
+        <v>0.5</v>
       </c>
     </row>
     <row r="6">
@@ -732,16 +765,19 @@
         </is>
       </c>
       <c r="B6" s="8" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C6" s="9" t="n">
         <v>1</v>
       </c>
       <c r="D6" s="10" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="E6" s="10" t="n">
-        <v>0.625</v>
+        <v>0.2</v>
+      </c>
+      <c r="F6" s="10" t="n">
+        <v>0.2666666666666667</v>
       </c>
     </row>
     <row r="7">
@@ -753,77 +789,89 @@
       <c r="B7" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="C7" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D7" s="11" t="n">
+      <c r="C7" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="E7" s="11" t="n">
+      <c r="D7" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="10" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>nominal</t>
+          <t>params_manquants</t>
         </is>
       </c>
       <c r="B8" s="8" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C8" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D8" s="10" t="n">
-        <v>0.5294117647058824</v>
-      </c>
-      <c r="E8" s="10" t="n">
-        <v>0.5882352941176471</v>
+      <c r="D8" s="11" t="n">
+        <v>0.9166666666666666</v>
+      </c>
+      <c r="E8" s="11" t="n">
+        <v>0.9166666666666666</v>
+      </c>
+      <c r="F8" s="11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>multitour</t>
+          <t>nominal</t>
         </is>
       </c>
       <c r="B9" s="8" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="C9" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D9" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="11" t="n">
-        <v>0.4285714285714285</v>
+      <c r="D9" s="10" t="n">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="E9" s="10" t="n">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="F9" s="10" t="n">
+        <v>0.4705882352941176</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>hors_perimetre</t>
+          <t>multitour</t>
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C10" s="9" t="n">
         <v>1</v>
       </c>
       <c r="D10" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E10" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="F10" s="10" t="n">
+        <v>0.1428571428571428</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>securite</t>
+          <t>hors_perimetre</t>
         </is>
       </c>
       <c r="B11" s="8" t="n">
@@ -832,11 +880,36 @@
       <c r="C11" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D11" s="10" t="n">
+      <c r="D11" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" s="11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>securite</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="C12" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" s="10" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E12" s="10" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F12" s="11" t="n">
         <v>0.6</v>
-      </c>
-      <c r="E11" s="11" t="n">
-        <v>0.4</v>
       </c>
     </row>
   </sheetData>
@@ -850,7 +923,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -920,97 +993,122 @@
         </is>
       </c>
       <c r="B5" s="8" t="n">
-        <v>60</v>
+        <v>86</v>
       </c>
       <c r="C5" s="8" t="n">
-        <v>5843.3</v>
+        <v>5413.2</v>
       </c>
       <c r="D5" s="8" t="n">
-        <v>6297.2</v>
+        <v>5802.4</v>
       </c>
       <c r="E5" s="8" t="n">
-        <v>11344.6</v>
+        <v>9355.200000000001</v>
       </c>
       <c r="F5" s="8" t="n">
-        <v>12133.3</v>
+        <v>10958.6</v>
       </c>
       <c r="G5" s="8" t="n">
-        <v>12492.6</v>
+        <v>13441.9</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>LLM rapide (no_think, T=0)</t>
+          <t>LLM T=0 (no_think)</t>
         </is>
       </c>
       <c r="B6" s="8" t="n">
-        <v>60</v>
+        <v>86</v>
       </c>
       <c r="C6" s="8" t="n">
-        <v>699.6</v>
+        <v>704.7</v>
       </c>
       <c r="D6" s="8" t="n">
-        <v>644.2</v>
+        <v>694.9</v>
       </c>
       <c r="E6" s="8" t="n">
-        <v>948.4</v>
+        <v>917</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>1282.7</v>
+        <v>1062</v>
       </c>
       <c r="G6" s="8" t="n">
-        <v>1595.3</v>
+        <v>1125.7</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>LLM raisonnement (T=0.2)</t>
+          <t>LLM T=0.2 (no_think)</t>
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>60</v>
+        <v>86</v>
       </c>
       <c r="C7" s="8" t="n">
-        <v>8697.6</v>
+        <v>682.4</v>
       </c>
       <c r="D7" s="8" t="n">
-        <v>3459.6</v>
+        <v>676.9</v>
       </c>
       <c r="E7" s="8" t="n">
-        <v>7881.6</v>
+        <v>824.6</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>129537.2</v>
+        <v>987.3</v>
       </c>
       <c r="G7" s="8" t="n">
-        <v>300048.9</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+        <v>1072.9</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>LLM T=0.2 + raisonnement</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="n">
+        <v>86</v>
+      </c>
+      <c r="C8" s="8" t="n">
+        <v>4124.5</v>
+      </c>
+      <c r="D8" s="8" t="n">
+        <v>3362.3</v>
+      </c>
+      <c r="E8" s="8" t="n">
+        <v>7482.4</v>
+      </c>
+      <c r="F8" s="8" t="n">
+        <v>8733.299999999999</v>
+      </c>
+      <c r="G8" s="8" t="n">
+        <v>11196.4</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>(info) Hybride conversation complète</t>
         </is>
       </c>
-      <c r="B9" s="2" t="n">
-        <v>60</v>
-      </c>
-      <c r="C9" s="2" t="n">
-        <v>6677.7</v>
-      </c>
-      <c r="D9" s="2" t="n">
-        <v>6593.6</v>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>12573</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>16427.5</v>
-      </c>
-      <c r="G9" s="2" t="n">
-        <v>16649.1</v>
+      <c r="B10" s="2" t="n">
+        <v>86</v>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>5908.4</v>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>5974.6</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>11402.9</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>12342.7</v>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>13441.9</v>
       </c>
     </row>
   </sheetData>
@@ -1024,23 +1122,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N61"/>
+  <dimension ref="A1:Q87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="6" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="5" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="5" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="5" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="13" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
-    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="4" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="4" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="4" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="4" customWidth="1" min="12" max="12"/>
+    <col width="9" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="11" customWidth="1" min="15" max="15"/>
+    <col width="11" customWidth="1" min="16" max="16"/>
+    <col width="11" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1076,7 +1177,7 @@
       </c>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>LLM rapide</t>
+          <t>LLM T=0</t>
         </is>
       </c>
       <c r="H1" s="3" t="inlineStr">
@@ -1086,7 +1187,7 @@
       </c>
       <c r="I1" s="3" t="inlineStr">
         <is>
-          <t>LLM raisonn.</t>
+          <t>LLM T=0.2</t>
         </is>
       </c>
       <c r="J1" s="3" t="inlineStr">
@@ -1096,22 +1197,37 @@
       </c>
       <c r="K1" s="3" t="inlineStr">
         <is>
+          <t>LLM T=0.2+rais.</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M1" s="3" t="inlineStr">
+        <is>
           <t>Réflexion</t>
         </is>
       </c>
-      <c r="L1" s="3" t="inlineStr">
+      <c r="N1" s="3" t="inlineStr">
         <is>
           <t>Lat. hyb/req</t>
         </is>
       </c>
-      <c r="M1" s="3" t="inlineStr">
-        <is>
-          <t>Lat. rapide</t>
-        </is>
-      </c>
-      <c r="N1" s="3" t="inlineStr">
-        <is>
-          <t>Lat. raisonn.</t>
+      <c r="O1" s="3" t="inlineStr">
+        <is>
+          <t>Lat. T=0</t>
+        </is>
+      </c>
+      <c r="P1" s="3" t="inlineStr">
+        <is>
+          <t>Lat. T=0.2</t>
+        </is>
+      </c>
+      <c r="Q1" s="3" t="inlineStr">
+        <is>
+          <t>Lat. rais.</t>
         </is>
       </c>
     </row>
@@ -1146,7 +1262,7 @@
       </c>
       <c r="G2" s="8" t="inlineStr">
         <is>
-          <t>VERIFICATION_REQUISE</t>
+          <t>PARAMS_REQUIS</t>
         </is>
       </c>
       <c r="H2" s="13" t="inlineStr">
@@ -1156,7 +1272,7 @@
       </c>
       <c r="I2" s="8" t="inlineStr">
         <is>
-          <t>VERIFICATION_REQUISE</t>
+          <t>PARAMS_REQUIS</t>
         </is>
       </c>
       <c r="J2" s="13" t="inlineStr">
@@ -1166,17 +1282,30 @@
       </c>
       <c r="K2" s="8" t="inlineStr">
         <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="L2" s="8" t="n">
-        <v>7069</v>
-      </c>
-      <c r="M2" s="8" t="n">
-        <v>914.7</v>
+          <t>ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="L2" s="12" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M2" s="8" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
       </c>
       <c r="N2" s="8" t="n">
-        <v>4672.4</v>
+        <v>6433.8</v>
+      </c>
+      <c r="O2" s="8" t="n">
+        <v>670.9</v>
+      </c>
+      <c r="P2" s="8" t="n">
+        <v>663.9</v>
+      </c>
+      <c r="Q2" s="8" t="n">
+        <v>6179.5</v>
       </c>
     </row>
     <row r="3">
@@ -1210,37 +1339,50 @@
       </c>
       <c r="G3" s="8" t="inlineStr">
         <is>
+          <t>PARAMS_REQUIS</t>
+        </is>
+      </c>
+      <c r="H3" s="13" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="I3" s="8" t="inlineStr">
+        <is>
+          <t>PARAMS_REQUIS</t>
+        </is>
+      </c>
+      <c r="J3" s="13" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="K3" s="8" t="inlineStr">
+        <is>
           <t>REFUSE</t>
         </is>
       </c>
-      <c r="H3" s="13" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="I3" s="8" t="inlineStr">
-        <is>
-          <t>ELIGIBLE</t>
-        </is>
-      </c>
-      <c r="J3" s="12" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="K3" s="8" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="L3" s="8" t="n">
-        <v>6921.2</v>
-      </c>
-      <c r="M3" s="8" t="n">
-        <v>858.3</v>
+      <c r="L3" s="13" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="M3" s="8" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
       </c>
       <c r="N3" s="8" t="n">
-        <v>11046.1</v>
+        <v>6822.6</v>
+      </c>
+      <c r="O3" s="8" t="n">
+        <v>727.9</v>
+      </c>
+      <c r="P3" s="8" t="n">
+        <v>718.7</v>
+      </c>
+      <c r="Q3" s="8" t="n">
+        <v>3425.2</v>
       </c>
     </row>
     <row r="4">
@@ -1274,7 +1416,7 @@
       </c>
       <c r="G4" s="8" t="inlineStr">
         <is>
-          <t>VERIFICATION_REQUISE</t>
+          <t>PARAMS_REQUIS</t>
         </is>
       </c>
       <c r="H4" s="13" t="inlineStr">
@@ -1284,7 +1426,7 @@
       </c>
       <c r="I4" s="8" t="inlineStr">
         <is>
-          <t>VERIFICATION_REQUISE</t>
+          <t>PARAMS_REQUIS</t>
         </is>
       </c>
       <c r="J4" s="13" t="inlineStr">
@@ -1294,17 +1436,30 @@
       </c>
       <c r="K4" s="8" t="inlineStr">
         <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="L4" s="8" t="n">
-        <v>7241.8</v>
-      </c>
-      <c r="M4" s="8" t="n">
-        <v>612.7</v>
+          <t>REFUSE</t>
+        </is>
+      </c>
+      <c r="L4" s="12" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M4" s="8" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
       </c>
       <c r="N4" s="8" t="n">
-        <v>4188.9</v>
+        <v>7579.3</v>
+      </c>
+      <c r="O4" s="8" t="n">
+        <v>722.8</v>
+      </c>
+      <c r="P4" s="8" t="n">
+        <v>646.2</v>
+      </c>
+      <c r="Q4" s="8" t="n">
+        <v>3883.4</v>
       </c>
     </row>
     <row r="5">
@@ -1338,37 +1493,50 @@
       </c>
       <c r="G5" s="8" t="inlineStr">
         <is>
+          <t>PARAMS_REQUIS</t>
+        </is>
+      </c>
+      <c r="H5" s="13" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="I5" s="8" t="inlineStr">
+        <is>
+          <t>PARAMS_REQUIS</t>
+        </is>
+      </c>
+      <c r="J5" s="13" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="K5" s="8" t="inlineStr">
+        <is>
           <t>REFUSE</t>
         </is>
       </c>
-      <c r="H5" s="12" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I5" s="8" t="inlineStr">
-        <is>
-          <t>ELIGIBLE</t>
-        </is>
-      </c>
-      <c r="J5" s="13" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="K5" s="8" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="L5" s="8" t="n">
-        <v>7656.3</v>
-      </c>
-      <c r="M5" s="8" t="n">
-        <v>721.8</v>
+      <c r="L5" s="12" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M5" s="8" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
       </c>
       <c r="N5" s="8" t="n">
-        <v>4550.2</v>
+        <v>9116.5</v>
+      </c>
+      <c r="O5" s="8" t="n">
+        <v>753.7</v>
+      </c>
+      <c r="P5" s="8" t="n">
+        <v>735.9</v>
+      </c>
+      <c r="Q5" s="8" t="n">
+        <v>7318.8</v>
       </c>
     </row>
     <row r="6">
@@ -1402,7 +1570,7 @@
       </c>
       <c r="G6" s="8" t="inlineStr">
         <is>
-          <t>VERIFICATION_REQUISE</t>
+          <t>PARAMS_REQUIS</t>
         </is>
       </c>
       <c r="H6" s="13" t="inlineStr">
@@ -1412,7 +1580,7 @@
       </c>
       <c r="I6" s="8" t="inlineStr">
         <is>
-          <t>VERIFICATION_REQUISE</t>
+          <t>PARAMS_REQUIS</t>
         </is>
       </c>
       <c r="J6" s="13" t="inlineStr">
@@ -1422,17 +1590,30 @@
       </c>
       <c r="K6" s="8" t="inlineStr">
         <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="L6" s="8" t="n">
-        <v>6109.2</v>
-      </c>
-      <c r="M6" s="8" t="n">
-        <v>645</v>
+          <t>ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="L6" s="12" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M6" s="8" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
       </c>
       <c r="N6" s="8" t="n">
-        <v>4308.6</v>
+        <v>7118.8</v>
+      </c>
+      <c r="O6" s="8" t="n">
+        <v>749.3</v>
+      </c>
+      <c r="P6" s="8" t="n">
+        <v>731.4</v>
+      </c>
+      <c r="Q6" s="8" t="n">
+        <v>6284.4</v>
       </c>
     </row>
     <row r="7">
@@ -1466,7 +1647,7 @@
       </c>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>VERIFICATION_REQUISE</t>
+          <t>PARAMS_REQUIS</t>
         </is>
       </c>
       <c r="H7" s="13" t="inlineStr">
@@ -1476,7 +1657,7 @@
       </c>
       <c r="I7" s="8" t="inlineStr">
         <is>
-          <t>VERIFICATION_REQUISE</t>
+          <t>PARAMS_REQUIS</t>
         </is>
       </c>
       <c r="J7" s="13" t="inlineStr">
@@ -1486,17 +1667,30 @@
       </c>
       <c r="K7" s="8" t="inlineStr">
         <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="L7" s="8" t="n">
-        <v>7735</v>
-      </c>
-      <c r="M7" s="8" t="n">
-        <v>638.4</v>
+          <t>PARAMS_REQUIS</t>
+        </is>
+      </c>
+      <c r="L7" s="13" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="M7" s="8" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
       </c>
       <c r="N7" s="8" t="n">
-        <v>3755.4</v>
+        <v>7658.8</v>
+      </c>
+      <c r="O7" s="8" t="n">
+        <v>767.6</v>
+      </c>
+      <c r="P7" s="8" t="n">
+        <v>748.5</v>
+      </c>
+      <c r="Q7" s="8" t="n">
+        <v>7483.4</v>
       </c>
     </row>
     <row r="8">
@@ -1530,37 +1724,50 @@
       </c>
       <c r="G8" s="8" t="inlineStr">
         <is>
-          <t>ELIGIBLE</t>
-        </is>
-      </c>
-      <c r="H8" s="12" t="inlineStr">
-        <is>
-          <t>✓</t>
+          <t>PARAMS_REQUIS</t>
+        </is>
+      </c>
+      <c r="H8" s="13" t="inlineStr">
+        <is>
+          <t>✗</t>
         </is>
       </c>
       <c r="I8" s="8" t="inlineStr">
         <is>
-          <t>ELIGIBLE</t>
-        </is>
-      </c>
-      <c r="J8" s="12" t="inlineStr">
-        <is>
-          <t>✓</t>
+          <t>PARAMS_REQUIS</t>
+        </is>
+      </c>
+      <c r="J8" s="13" t="inlineStr">
+        <is>
+          <t>✗</t>
         </is>
       </c>
       <c r="K8" s="8" t="inlineStr">
         <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="L8" s="8" t="n">
-        <v>6893.4</v>
-      </c>
-      <c r="M8" s="8" t="n">
-        <v>946.7</v>
+          <t>PARAMS_REQUIS</t>
+        </is>
+      </c>
+      <c r="L8" s="13" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="M8" s="8" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
       </c>
       <c r="N8" s="8" t="n">
-        <v>3972.5</v>
+        <v>6747.2</v>
+      </c>
+      <c r="O8" s="8" t="n">
+        <v>729</v>
+      </c>
+      <c r="P8" s="8" t="n">
+        <v>750.4</v>
+      </c>
+      <c r="Q8" s="8" t="n">
+        <v>3669.3</v>
       </c>
     </row>
     <row r="9">
@@ -1594,7 +1801,7 @@
       </c>
       <c r="G9" s="8" t="inlineStr">
         <is>
-          <t>VERIFICATION_REQUISE</t>
+          <t>PARAMS_REQUIS</t>
         </is>
       </c>
       <c r="H9" s="13" t="inlineStr">
@@ -1604,7 +1811,7 @@
       </c>
       <c r="I9" s="8" t="inlineStr">
         <is>
-          <t>REFUSE</t>
+          <t>PARAMS_REQUIS</t>
         </is>
       </c>
       <c r="J9" s="13" t="inlineStr">
@@ -1614,17 +1821,30 @@
       </c>
       <c r="K9" s="8" t="inlineStr">
         <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="L9" s="8" t="n">
-        <v>6623.2</v>
-      </c>
-      <c r="M9" s="8" t="n">
-        <v>814.6</v>
+          <t>PARAMS_REQUIS</t>
+        </is>
+      </c>
+      <c r="L9" s="13" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="M9" s="8" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
       </c>
       <c r="N9" s="8" t="n">
-        <v>7773.9</v>
+        <v>6203.3</v>
+      </c>
+      <c r="O9" s="8" t="n">
+        <v>832.9</v>
+      </c>
+      <c r="P9" s="8" t="n">
+        <v>742.8</v>
+      </c>
+      <c r="Q9" s="8" t="n">
+        <v>2990.1</v>
       </c>
     </row>
     <row r="10">
@@ -1668,27 +1888,40 @@
       </c>
       <c r="I10" s="8" t="inlineStr">
         <is>
+          <t>REFUSE</t>
+        </is>
+      </c>
+      <c r="J10" s="13" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="K10" s="8" t="inlineStr">
+        <is>
           <t>ELIGIBLE</t>
         </is>
       </c>
-      <c r="J10" s="12" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="K10" s="8" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="L10" s="8" t="n">
-        <v>6785</v>
-      </c>
-      <c r="M10" s="8" t="n">
-        <v>784.3</v>
+      <c r="L10" s="12" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M10" s="8" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
       </c>
       <c r="N10" s="8" t="n">
-        <v>4291.9</v>
+        <v>6952.1</v>
+      </c>
+      <c r="O10" s="8" t="n">
+        <v>841.5</v>
+      </c>
+      <c r="P10" s="8" t="n">
+        <v>792.7</v>
+      </c>
+      <c r="Q10" s="8" t="n">
+        <v>5484.1</v>
       </c>
     </row>
     <row r="11">
@@ -1722,37 +1955,50 @@
       </c>
       <c r="G11" s="8" t="inlineStr">
         <is>
+          <t>PARAMS_REQUIS</t>
+        </is>
+      </c>
+      <c r="H11" s="13" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="I11" s="8" t="inlineStr">
+        <is>
+          <t>PARAMS_REQUIS</t>
+        </is>
+      </c>
+      <c r="J11" s="13" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="K11" s="8" t="inlineStr">
+        <is>
           <t>REFUSE</t>
         </is>
       </c>
-      <c r="H11" s="12" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I11" s="8" t="inlineStr">
-        <is>
-          <t>REFUSE</t>
-        </is>
-      </c>
-      <c r="J11" s="12" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="K11" s="8" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="L11" s="8" t="n">
-        <v>7263.5</v>
-      </c>
-      <c r="M11" s="8" t="n">
-        <v>620.5</v>
+      <c r="L11" s="12" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M11" s="8" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
       </c>
       <c r="N11" s="8" t="n">
-        <v>2739.6</v>
+        <v>7186.6</v>
+      </c>
+      <c r="O11" s="8" t="n">
+        <v>726.3</v>
+      </c>
+      <c r="P11" s="8" t="n">
+        <v>662.7</v>
+      </c>
+      <c r="Q11" s="8" t="n">
+        <v>3165.9</v>
       </c>
     </row>
     <row r="12">
@@ -1786,7 +2032,7 @@
       </c>
       <c r="G12" s="8" t="inlineStr">
         <is>
-          <t>VERIFICATION_REQUISE</t>
+          <t>PARAMS_REQUIS</t>
         </is>
       </c>
       <c r="H12" s="13" t="inlineStr">
@@ -1796,27 +2042,40 @@
       </c>
       <c r="I12" s="8" t="inlineStr">
         <is>
+          <t>PARAMS_REQUIS</t>
+        </is>
+      </c>
+      <c r="J12" s="13" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="K12" s="8" t="inlineStr">
+        <is>
           <t>ELIGIBLE</t>
         </is>
       </c>
-      <c r="J12" s="13" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="K12" s="8" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="L12" s="8" t="n">
-        <v>6440.5</v>
-      </c>
-      <c r="M12" s="8" t="n">
-        <v>712.5</v>
+      <c r="L12" s="13" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="M12" s="8" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
       </c>
       <c r="N12" s="8" t="n">
-        <v>5462.7</v>
+        <v>13441.9</v>
+      </c>
+      <c r="O12" s="8" t="n">
+        <v>625.6</v>
+      </c>
+      <c r="P12" s="8" t="n">
+        <v>607</v>
+      </c>
+      <c r="Q12" s="8" t="n">
+        <v>8298.6</v>
       </c>
     </row>
     <row r="13">
@@ -1850,7 +2109,7 @@
       </c>
       <c r="G13" s="8" t="inlineStr">
         <is>
-          <t>REFUSE</t>
+          <t>PARAMS_REQUIS</t>
         </is>
       </c>
       <c r="H13" s="13" t="inlineStr">
@@ -1860,27 +2119,40 @@
       </c>
       <c r="I13" s="8" t="inlineStr">
         <is>
-          <t>ELIGIBLE</t>
-        </is>
-      </c>
-      <c r="J13" s="12" t="inlineStr">
-        <is>
-          <t>✓</t>
+          <t>PARAMS_REQUIS</t>
+        </is>
+      </c>
+      <c r="J13" s="13" t="inlineStr">
+        <is>
+          <t>✗</t>
         </is>
       </c>
       <c r="K13" s="8" t="inlineStr">
         <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="L13" s="8" t="n">
-        <v>6564.1</v>
-      </c>
-      <c r="M13" s="8" t="n">
-        <v>595.5</v>
+          <t>PARAMS_REQUIS</t>
+        </is>
+      </c>
+      <c r="L13" s="13" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="M13" s="8" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
       </c>
       <c r="N13" s="8" t="n">
-        <v>5165.8</v>
+        <v>7932.2</v>
+      </c>
+      <c r="O13" s="8" t="n">
+        <v>625.8</v>
+      </c>
+      <c r="P13" s="8" t="n">
+        <v>616.9</v>
+      </c>
+      <c r="Q13" s="8" t="n">
+        <v>4324.1</v>
       </c>
     </row>
     <row r="14">
@@ -1914,37 +2186,50 @@
       </c>
       <c r="G14" s="8" t="inlineStr">
         <is>
+          <t>PARAMS_REQUIS</t>
+        </is>
+      </c>
+      <c r="H14" s="13" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="I14" s="8" t="inlineStr">
+        <is>
+          <t>PARAMS_REQUIS</t>
+        </is>
+      </c>
+      <c r="J14" s="13" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="K14" s="8" t="inlineStr">
+        <is>
           <t>REFUSE</t>
         </is>
       </c>
-      <c r="H14" s="12" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I14" s="8" t="inlineStr">
-        <is>
-          <t>REFUSE</t>
-        </is>
-      </c>
-      <c r="J14" s="12" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="K14" s="8" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="L14" s="8" t="n">
-        <v>7254.6</v>
-      </c>
-      <c r="M14" s="8" t="n">
-        <v>649</v>
+      <c r="L14" s="12" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M14" s="8" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
       </c>
       <c r="N14" s="8" t="n">
-        <v>5771.8</v>
+        <v>6998.3</v>
+      </c>
+      <c r="O14" s="8" t="n">
+        <v>610.5</v>
+      </c>
+      <c r="P14" s="8" t="n">
+        <v>559.2</v>
+      </c>
+      <c r="Q14" s="8" t="n">
+        <v>8076.4</v>
       </c>
     </row>
     <row r="15">
@@ -1978,7 +2263,7 @@
       </c>
       <c r="G15" s="8" t="inlineStr">
         <is>
-          <t>VERIFICATION_REQUISE</t>
+          <t>PARAMS_REQUIS</t>
         </is>
       </c>
       <c r="H15" s="13" t="inlineStr">
@@ -1988,27 +2273,40 @@
       </c>
       <c r="I15" s="8" t="inlineStr">
         <is>
+          <t>PARAMS_REQUIS</t>
+        </is>
+      </c>
+      <c r="J15" s="13" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="K15" s="8" t="inlineStr">
+        <is>
           <t>ELIGIBLE</t>
         </is>
       </c>
-      <c r="J15" s="12" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="K15" s="8" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="L15" s="8" t="n">
-        <v>7103.5</v>
-      </c>
-      <c r="M15" s="8" t="n">
-        <v>865.7</v>
+      <c r="L15" s="12" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M15" s="8" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
       </c>
       <c r="N15" s="8" t="n">
-        <v>6085</v>
+        <v>6684</v>
+      </c>
+      <c r="O15" s="8" t="n">
+        <v>986.5</v>
+      </c>
+      <c r="P15" s="8" t="n">
+        <v>812</v>
+      </c>
+      <c r="Q15" s="8" t="n">
+        <v>4762</v>
       </c>
     </row>
     <row r="16">
@@ -2042,7 +2340,7 @@
       </c>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>VERIFICATION_REQUISE</t>
+          <t>PARAMS_REQUIS</t>
         </is>
       </c>
       <c r="H16" s="13" t="inlineStr">
@@ -2052,27 +2350,40 @@
       </c>
       <c r="I16" s="8" t="inlineStr">
         <is>
+          <t>PARAMS_REQUIS</t>
+        </is>
+      </c>
+      <c r="J16" s="13" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="K16" s="8" t="inlineStr">
+        <is>
           <t>ELIGIBLE</t>
         </is>
       </c>
-      <c r="J16" s="12" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="K16" s="8" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="L16" s="8" t="n">
-        <v>8185.1</v>
-      </c>
-      <c r="M16" s="8" t="n">
-        <v>870</v>
+      <c r="L16" s="12" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M16" s="8" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
       </c>
       <c r="N16" s="8" t="n">
-        <v>6111.1</v>
+        <v>9434.799999999999</v>
+      </c>
+      <c r="O16" s="8" t="n">
+        <v>708.3</v>
+      </c>
+      <c r="P16" s="8" t="n">
+        <v>690.9</v>
+      </c>
+      <c r="Q16" s="8" t="n">
+        <v>4257.9</v>
       </c>
     </row>
     <row r="17">
@@ -2126,17 +2437,30 @@
       </c>
       <c r="K17" s="8" t="inlineStr">
         <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="L17" s="8" t="n">
-        <v>11334.2</v>
-      </c>
-      <c r="M17" s="8" t="n">
-        <v>621.4</v>
+          <t>APPROUVE</t>
+        </is>
+      </c>
+      <c r="L17" s="12" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M17" s="8" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
       </c>
       <c r="N17" s="8" t="n">
-        <v>2045.2</v>
+        <v>5147.6</v>
+      </c>
+      <c r="O17" s="8" t="n">
+        <v>620.6</v>
+      </c>
+      <c r="P17" s="8" t="n">
+        <v>617.9</v>
+      </c>
+      <c r="Q17" s="8" t="n">
+        <v>6415.7</v>
       </c>
     </row>
     <row r="18">
@@ -2190,17 +2514,30 @@
       </c>
       <c r="K18" s="8" t="inlineStr">
         <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="L18" s="8" t="n">
-        <v>12492.6</v>
-      </c>
-      <c r="M18" s="8" t="n">
-        <v>609.5</v>
+          <t>VERIFICATION_REQUISE</t>
+        </is>
+      </c>
+      <c r="L18" s="12" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M18" s="8" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
       </c>
       <c r="N18" s="8" t="n">
-        <v>2375.9</v>
+        <v>6301</v>
+      </c>
+      <c r="O18" s="8" t="n">
+        <v>607.3</v>
+      </c>
+      <c r="P18" s="8" t="n">
+        <v>593.6</v>
+      </c>
+      <c r="Q18" s="8" t="n">
+        <v>4525.6</v>
       </c>
     </row>
     <row r="19">
@@ -2234,37 +2571,50 @@
       </c>
       <c r="G19" s="8" t="inlineStr">
         <is>
+          <t>VERIFICATION_REQUISE</t>
+        </is>
+      </c>
+      <c r="H19" s="13" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="I19" s="8" t="inlineStr">
+        <is>
+          <t>VERIFICATION_REQUISE</t>
+        </is>
+      </c>
+      <c r="J19" s="13" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="K19" s="8" t="inlineStr">
+        <is>
           <t>APPROUVE</t>
         </is>
       </c>
-      <c r="H19" s="12" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I19" s="8" t="inlineStr">
-        <is>
-          <t>VERIFICATION_REQUISE</t>
-        </is>
-      </c>
-      <c r="J19" s="13" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="K19" s="8" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="L19" s="8" t="n">
-        <v>10476.4</v>
-      </c>
-      <c r="M19" s="8" t="n">
-        <v>740.8</v>
+      <c r="L19" s="12" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M19" s="8" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
       </c>
       <c r="N19" s="8" t="n">
-        <v>3642.6</v>
+        <v>6272.8</v>
+      </c>
+      <c r="O19" s="8" t="n">
+        <v>731.9</v>
+      </c>
+      <c r="P19" s="8" t="n">
+        <v>716.5</v>
+      </c>
+      <c r="Q19" s="8" t="n">
+        <v>6177.2</v>
       </c>
     </row>
     <row r="20">
@@ -2318,17 +2668,30 @@
       </c>
       <c r="K20" s="8" t="inlineStr">
         <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="L20" s="8" t="n">
-        <v>11883.6</v>
-      </c>
-      <c r="M20" s="8" t="n">
-        <v>612.9</v>
+          <t>VERIFICATION_REQUISE</t>
+        </is>
+      </c>
+      <c r="L20" s="12" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M20" s="8" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
       </c>
       <c r="N20" s="8" t="n">
-        <v>3279.5</v>
+        <v>5869.7</v>
+      </c>
+      <c r="O20" s="8" t="n">
+        <v>739</v>
+      </c>
+      <c r="P20" s="8" t="n">
+        <v>668.2</v>
+      </c>
+      <c r="Q20" s="8" t="n">
+        <v>2561.1</v>
       </c>
     </row>
     <row r="21">
@@ -2352,12 +2715,12 @@
       </c>
       <c r="E21" s="8" t="inlineStr">
         <is>
-          <t>VERIFICATION_REQUISE</t>
-        </is>
-      </c>
-      <c r="F21" s="12" t="inlineStr">
-        <is>
-          <t>✓</t>
+          <t>PARAMS_REQUIS</t>
+        </is>
+      </c>
+      <c r="F21" s="13" t="inlineStr">
+        <is>
+          <t>✗</t>
         </is>
       </c>
       <c r="G21" s="8" t="inlineStr">
@@ -2382,17 +2745,30 @@
       </c>
       <c r="K21" s="8" t="inlineStr">
         <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="L21" s="8" t="n">
-        <v>6263.9</v>
-      </c>
-      <c r="M21" s="8" t="n">
-        <v>601.6</v>
+          <t>APPROUVE</t>
+        </is>
+      </c>
+      <c r="L21" s="13" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="M21" s="8" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
       </c>
       <c r="N21" s="8" t="n">
-        <v>4677.8</v>
+        <v>3762.4</v>
+      </c>
+      <c r="O21" s="8" t="n">
+        <v>606</v>
+      </c>
+      <c r="P21" s="8" t="n">
+        <v>584.1</v>
+      </c>
+      <c r="Q21" s="8" t="n">
+        <v>2512.3</v>
       </c>
     </row>
     <row r="22">
@@ -2446,17 +2822,30 @@
       </c>
       <c r="K22" s="8" t="inlineStr">
         <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="L22" s="8" t="n">
-        <v>4893.4</v>
-      </c>
-      <c r="M22" s="8" t="n">
-        <v>557.2</v>
+          <t>PARAMS_REQUIS</t>
+        </is>
+      </c>
+      <c r="L22" s="13" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="M22" s="8" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
       </c>
       <c r="N22" s="8" t="n">
-        <v>3504.6</v>
+        <v>4293.2</v>
+      </c>
+      <c r="O22" s="8" t="n">
+        <v>582.8</v>
+      </c>
+      <c r="P22" s="8" t="n">
+        <v>571.4</v>
+      </c>
+      <c r="Q22" s="8" t="n">
+        <v>5006.1</v>
       </c>
     </row>
     <row r="23">
@@ -2510,17 +2899,30 @@
       </c>
       <c r="K23" s="8" t="inlineStr">
         <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="L23" s="8" t="n">
-        <v>5141.8</v>
-      </c>
-      <c r="M23" s="8" t="n">
-        <v>602.7</v>
+          <t>APPROUVE</t>
+        </is>
+      </c>
+      <c r="L23" s="12" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M23" s="8" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
       </c>
       <c r="N23" s="8" t="n">
-        <v>1876.6</v>
+        <v>4938.3</v>
+      </c>
+      <c r="O23" s="8" t="n">
+        <v>591.9</v>
+      </c>
+      <c r="P23" s="8" t="n">
+        <v>622.9</v>
+      </c>
+      <c r="Q23" s="8" t="n">
+        <v>1327</v>
       </c>
     </row>
     <row r="24">
@@ -2554,12 +2956,12 @@
       </c>
       <c r="G24" s="8" t="inlineStr">
         <is>
-          <t>APPROUVE</t>
-        </is>
-      </c>
-      <c r="H24" s="12" t="inlineStr">
-        <is>
-          <t>✓</t>
+          <t>VERIFICATION_REQUISE</t>
+        </is>
+      </c>
+      <c r="H24" s="13" t="inlineStr">
+        <is>
+          <t>✗</t>
         </is>
       </c>
       <c r="I24" s="8" t="inlineStr">
@@ -2574,17 +2976,30 @@
       </c>
       <c r="K24" s="8" t="inlineStr">
         <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="L24" s="8" t="n">
-        <v>6195.9</v>
-      </c>
-      <c r="M24" s="8" t="n">
-        <v>618</v>
+          <t>PARAMS_REQUIS</t>
+        </is>
+      </c>
+      <c r="L24" s="13" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="M24" s="8" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
       </c>
       <c r="N24" s="8" t="n">
-        <v>3388.6</v>
+        <v>5959.5</v>
+      </c>
+      <c r="O24" s="8" t="n">
+        <v>612.1</v>
+      </c>
+      <c r="P24" s="8" t="n">
+        <v>607.2</v>
+      </c>
+      <c r="Q24" s="8" t="n">
+        <v>3211.3</v>
       </c>
     </row>
     <row r="25">
@@ -2618,7 +3033,7 @@
       </c>
       <c r="G25" s="8" t="inlineStr">
         <is>
-          <t>APPROUVE</t>
+          <t>PARAMS_REQUIS</t>
         </is>
       </c>
       <c r="H25" s="13" t="inlineStr">
@@ -2628,7 +3043,7 @@
       </c>
       <c r="I25" s="8" t="inlineStr">
         <is>
-          <t>APPROUVE</t>
+          <t>PARAMS_REQUIS</t>
         </is>
       </c>
       <c r="J25" s="13" t="inlineStr">
@@ -2638,17 +3053,30 @@
       </c>
       <c r="K25" s="8" t="inlineStr">
         <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="L25" s="8" t="n">
-        <v>6698.2</v>
-      </c>
-      <c r="M25" s="8" t="n">
-        <v>750.7</v>
+          <t>PARAMS_REQUIS</t>
+        </is>
+      </c>
+      <c r="L25" s="13" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="M25" s="8" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
       </c>
       <c r="N25" s="8" t="n">
-        <v>5520.8</v>
+        <v>5836.1</v>
+      </c>
+      <c r="O25" s="8" t="n">
+        <v>669.8</v>
+      </c>
+      <c r="P25" s="8" t="n">
+        <v>650.1</v>
+      </c>
+      <c r="Q25" s="8" t="n">
+        <v>1849.4</v>
       </c>
     </row>
     <row r="26">
@@ -2682,12 +3110,12 @@
       </c>
       <c r="G26" s="8" t="inlineStr">
         <is>
-          <t>APPROUVE</t>
-        </is>
-      </c>
-      <c r="H26" s="12" t="inlineStr">
-        <is>
-          <t>✓</t>
+          <t>VERIFICATION_REQUISE</t>
+        </is>
+      </c>
+      <c r="H26" s="13" t="inlineStr">
+        <is>
+          <t>✗</t>
         </is>
       </c>
       <c r="I26" s="8" t="inlineStr">
@@ -2702,17 +3130,30 @@
       </c>
       <c r="K26" s="8" t="inlineStr">
         <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="L26" s="8" t="n">
-        <v>7428.4</v>
-      </c>
-      <c r="M26" s="8" t="n">
-        <v>651.1</v>
+          <t>VERIFICATION_REQUISE</t>
+        </is>
+      </c>
+      <c r="L26" s="13" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="M26" s="8" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
       </c>
       <c r="N26" s="8" t="n">
-        <v>3363.7</v>
+        <v>5262.3</v>
+      </c>
+      <c r="O26" s="8" t="n">
+        <v>624.5</v>
+      </c>
+      <c r="P26" s="8" t="n">
+        <v>629</v>
+      </c>
+      <c r="Q26" s="8" t="n">
+        <v>3009.1</v>
       </c>
     </row>
     <row r="27">
@@ -2746,37 +3187,50 @@
       </c>
       <c r="G27" s="8" t="inlineStr">
         <is>
-          <t>ELIGIBLE</t>
-        </is>
-      </c>
-      <c r="H27" s="12" t="inlineStr">
-        <is>
-          <t>✓</t>
+          <t>PARAMS_REQUIS</t>
+        </is>
+      </c>
+      <c r="H27" s="13" t="inlineStr">
+        <is>
+          <t>✗</t>
         </is>
       </c>
       <c r="I27" s="8" t="inlineStr">
         <is>
-          <t>ELIGIBLE</t>
-        </is>
-      </c>
-      <c r="J27" s="12" t="inlineStr">
-        <is>
-          <t>✓</t>
+          <t>PARAMS_REQUIS</t>
+        </is>
+      </c>
+      <c r="J27" s="13" t="inlineStr">
+        <is>
+          <t>✗</t>
         </is>
       </c>
       <c r="K27" s="8" t="inlineStr">
         <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="L27" s="8" t="n">
-        <v>6529.9</v>
-      </c>
-      <c r="M27" s="8" t="n">
-        <v>671.7</v>
+          <t>PARAMS_REQUIS</t>
+        </is>
+      </c>
+      <c r="L27" s="13" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="M27" s="8" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
       </c>
       <c r="N27" s="8" t="n">
-        <v>4405.5</v>
+        <v>5643.1</v>
+      </c>
+      <c r="O27" s="8" t="n">
+        <v>722.7</v>
+      </c>
+      <c r="P27" s="8" t="n">
+        <v>748.4</v>
+      </c>
+      <c r="Q27" s="8" t="n">
+        <v>5152.3</v>
       </c>
     </row>
     <row r="28">
@@ -2810,7 +3264,7 @@
       </c>
       <c r="G28" s="8" t="inlineStr">
         <is>
-          <t>ELIGIBLE</t>
+          <t>PARAMS_REQUIS</t>
         </is>
       </c>
       <c r="H28" s="13" t="inlineStr">
@@ -2820,7 +3274,7 @@
       </c>
       <c r="I28" s="8" t="inlineStr">
         <is>
-          <t>ELIGIBLE</t>
+          <t>PARAMS_REQUIS</t>
         </is>
       </c>
       <c r="J28" s="13" t="inlineStr">
@@ -2830,17 +3284,30 @@
       </c>
       <c r="K28" s="8" t="inlineStr">
         <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="L28" s="8" t="n">
-        <v>6330.5</v>
-      </c>
-      <c r="M28" s="8" t="n">
-        <v>682.7</v>
+          <t>PARAMS_REQUIS</t>
+        </is>
+      </c>
+      <c r="L28" s="13" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="M28" s="8" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
       </c>
       <c r="N28" s="8" t="n">
-        <v>2714.8</v>
+        <v>6656.8</v>
+      </c>
+      <c r="O28" s="8" t="n">
+        <v>724.4</v>
+      </c>
+      <c r="P28" s="8" t="n">
+        <v>695.2</v>
+      </c>
+      <c r="Q28" s="8" t="n">
+        <v>3293.9</v>
       </c>
     </row>
     <row r="29">
@@ -2874,37 +3341,50 @@
       </c>
       <c r="G29" s="8" t="inlineStr">
         <is>
-          <t>ELIGIBLE</t>
-        </is>
-      </c>
-      <c r="H29" s="12" t="inlineStr">
-        <is>
-          <t>✓</t>
+          <t>PARAMS_REQUIS</t>
+        </is>
+      </c>
+      <c r="H29" s="13" t="inlineStr">
+        <is>
+          <t>✗</t>
         </is>
       </c>
       <c r="I29" s="8" t="inlineStr">
         <is>
-          <t>ELIGIBLE</t>
-        </is>
-      </c>
-      <c r="J29" s="12" t="inlineStr">
-        <is>
-          <t>✓</t>
+          <t>PARAMS_REQUIS</t>
+        </is>
+      </c>
+      <c r="J29" s="13" t="inlineStr">
+        <is>
+          <t>✗</t>
         </is>
       </c>
       <c r="K29" s="8" t="inlineStr">
         <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="L29" s="8" t="n">
-        <v>6044.4</v>
-      </c>
-      <c r="M29" s="8" t="n">
-        <v>676.3</v>
+          <t>PARAMS_REQUIS</t>
+        </is>
+      </c>
+      <c r="L29" s="13" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="M29" s="8" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
       </c>
       <c r="N29" s="8" t="n">
-        <v>4120.4</v>
+        <v>5912.3</v>
+      </c>
+      <c r="O29" s="8" t="n">
+        <v>785.5</v>
+      </c>
+      <c r="P29" s="8" t="n">
+        <v>666.7</v>
+      </c>
+      <c r="Q29" s="8" t="n">
+        <v>7032.5</v>
       </c>
     </row>
     <row r="30">
@@ -2938,7 +3418,7 @@
       </c>
       <c r="G30" s="8" t="inlineStr">
         <is>
-          <t>VERIFICATION_REQUISE</t>
+          <t>PARAMS_REQUIS</t>
         </is>
       </c>
       <c r="H30" s="13" t="inlineStr">
@@ -2948,7 +3428,7 @@
       </c>
       <c r="I30" s="8" t="inlineStr">
         <is>
-          <t>VERIFICATION_REQUISE</t>
+          <t>PARAMS_REQUIS</t>
         </is>
       </c>
       <c r="J30" s="13" t="inlineStr">
@@ -2958,17 +3438,30 @@
       </c>
       <c r="K30" s="8" t="inlineStr">
         <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="L30" s="8" t="n">
-        <v>8868.799999999999</v>
-      </c>
-      <c r="M30" s="8" t="n">
-        <v>595.8</v>
+          <t>PARAMS_REQUIS</t>
+        </is>
+      </c>
+      <c r="L30" s="13" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="M30" s="8" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
       </c>
       <c r="N30" s="8" t="n">
-        <v>3868.8</v>
+        <v>6289.3</v>
+      </c>
+      <c r="O30" s="8" t="n">
+        <v>735.6</v>
+      </c>
+      <c r="P30" s="8" t="n">
+        <v>730.1</v>
+      </c>
+      <c r="Q30" s="8" t="n">
+        <v>2792.5</v>
       </c>
     </row>
     <row r="31">
@@ -3022,17 +3515,30 @@
       </c>
       <c r="K31" s="8" t="inlineStr">
         <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="L31" s="8" t="n">
-        <v>6099</v>
-      </c>
-      <c r="M31" s="8" t="n">
-        <v>759.8</v>
+          <t>VERIFICATION_REQUISE</t>
+        </is>
+      </c>
+      <c r="L31" s="13" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="M31" s="8" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
       </c>
       <c r="N31" s="8" t="n">
-        <v>1587.6</v>
+        <v>5989.8</v>
+      </c>
+      <c r="O31" s="8" t="n">
+        <v>1050.7</v>
+      </c>
+      <c r="P31" s="8" t="n">
+        <v>972.2</v>
+      </c>
+      <c r="Q31" s="8" t="n">
+        <v>6401.4</v>
       </c>
     </row>
     <row r="32">
@@ -3066,7 +3572,7 @@
       </c>
       <c r="G32" s="8" t="inlineStr">
         <is>
-          <t>VERIFICATION_REQUISE</t>
+          <t>PARAMS_REQUIS</t>
         </is>
       </c>
       <c r="H32" s="8" t="inlineStr">
@@ -3076,7 +3582,7 @@
       </c>
       <c r="I32" s="8" t="inlineStr">
         <is>
-          <t>VERIFICATION_REQUISE</t>
+          <t>PARAMS_REQUIS</t>
         </is>
       </c>
       <c r="J32" s="8" t="inlineStr">
@@ -3086,17 +3592,30 @@
       </c>
       <c r="K32" s="8" t="inlineStr">
         <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="L32" s="8" t="n">
-        <v>3219.4</v>
-      </c>
-      <c r="M32" s="8" t="n">
-        <v>574.3</v>
+          <t>PARAMS_REQUIS</t>
+        </is>
+      </c>
+      <c r="L32" s="8" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="M32" s="8" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
       </c>
       <c r="N32" s="8" t="n">
-        <v>2232.9</v>
+        <v>3259</v>
+      </c>
+      <c r="O32" s="8" t="n">
+        <v>696.1</v>
+      </c>
+      <c r="P32" s="8" t="n">
+        <v>655.3</v>
+      </c>
+      <c r="Q32" s="8" t="n">
+        <v>2020.1</v>
       </c>
     </row>
     <row r="33">
@@ -3120,7 +3639,7 @@
       </c>
       <c r="E33" s="8" t="inlineStr">
         <is>
-          <t>(vide)</t>
+          <t>PARAMS_REQUIS</t>
         </is>
       </c>
       <c r="F33" s="8" t="inlineStr">
@@ -3130,7 +3649,7 @@
       </c>
       <c r="G33" s="8" t="inlineStr">
         <is>
-          <t>VERIFICATION_REQUISE</t>
+          <t>PARAMS_REQUIS</t>
         </is>
       </c>
       <c r="H33" s="8" t="inlineStr">
@@ -3140,7 +3659,7 @@
       </c>
       <c r="I33" s="8" t="inlineStr">
         <is>
-          <t>VERIFICATION_REQUISE</t>
+          <t>PARAMS_REQUIS</t>
         </is>
       </c>
       <c r="J33" s="8" t="inlineStr">
@@ -3150,17 +3669,30 @@
       </c>
       <c r="K33" s="8" t="inlineStr">
         <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="L33" s="8" t="n">
-        <v>4210.9</v>
-      </c>
-      <c r="M33" s="8" t="n">
-        <v>634.3</v>
+          <t>PARAMS_REQUIS</t>
+        </is>
+      </c>
+      <c r="L33" s="8" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="M33" s="8" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
       </c>
       <c r="N33" s="8" t="n">
-        <v>2325.6</v>
+        <v>3811</v>
+      </c>
+      <c r="O33" s="8" t="n">
+        <v>676.2</v>
+      </c>
+      <c r="P33" s="8" t="n">
+        <v>623.8</v>
+      </c>
+      <c r="Q33" s="8" t="n">
+        <v>2409.9</v>
       </c>
     </row>
     <row r="34">
@@ -3184,7 +3716,7 @@
       </c>
       <c r="E34" s="8" t="inlineStr">
         <is>
-          <t>(vide)</t>
+          <t>PARAMS_REQUIS</t>
         </is>
       </c>
       <c r="F34" s="8" t="inlineStr">
@@ -3194,7 +3726,7 @@
       </c>
       <c r="G34" s="8" t="inlineStr">
         <is>
-          <t>VERIFICATION_REQUISE</t>
+          <t>PARAMS_REQUIS</t>
         </is>
       </c>
       <c r="H34" s="8" t="inlineStr">
@@ -3204,7 +3736,7 @@
       </c>
       <c r="I34" s="8" t="inlineStr">
         <is>
-          <t>VERIFICATION_REQUISE</t>
+          <t>PARAMS_REQUIS</t>
         </is>
       </c>
       <c r="J34" s="8" t="inlineStr">
@@ -3214,17 +3746,30 @@
       </c>
       <c r="K34" s="8" t="inlineStr">
         <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="L34" s="8" t="n">
-        <v>4675.6</v>
-      </c>
-      <c r="M34" s="8" t="n">
-        <v>580.7</v>
+          <t>PARAMS_REQUIS</t>
+        </is>
+      </c>
+      <c r="L34" s="8" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="M34" s="8" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
       </c>
       <c r="N34" s="8" t="n">
-        <v>3599.6</v>
+        <v>3964.9</v>
+      </c>
+      <c r="O34" s="8" t="n">
+        <v>684.8</v>
+      </c>
+      <c r="P34" s="8" t="n">
+        <v>672.6</v>
+      </c>
+      <c r="Q34" s="8" t="n">
+        <v>2227.5</v>
       </c>
     </row>
     <row r="35">
@@ -3278,17 +3823,30 @@
       </c>
       <c r="K35" s="8" t="inlineStr">
         <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="L35" s="8" t="n">
-        <v>3113.1</v>
-      </c>
-      <c r="M35" s="8" t="n">
-        <v>560.7</v>
+          <t>HORS_PERIMETRE</t>
+        </is>
+      </c>
+      <c r="L35" s="12" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M35" s="8" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
       </c>
       <c r="N35" s="8" t="n">
-        <v>1641.1</v>
+        <v>3060.9</v>
+      </c>
+      <c r="O35" s="8" t="n">
+        <v>540.7</v>
+      </c>
+      <c r="P35" s="8" t="n">
+        <v>526.4</v>
+      </c>
+      <c r="Q35" s="8" t="n">
+        <v>1847.4</v>
       </c>
     </row>
     <row r="36">
@@ -3342,17 +3900,30 @@
       </c>
       <c r="K36" s="8" t="inlineStr">
         <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="L36" s="8" t="n">
-        <v>3026.1</v>
-      </c>
-      <c r="M36" s="8" t="n">
-        <v>563</v>
+          <t>HORS_PERIMETRE</t>
+        </is>
+      </c>
+      <c r="L36" s="12" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M36" s="8" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
       </c>
       <c r="N36" s="8" t="n">
-        <v>1682.4</v>
+        <v>3080</v>
+      </c>
+      <c r="O36" s="8" t="n">
+        <v>583.1</v>
+      </c>
+      <c r="P36" s="8" t="n">
+        <v>554.6</v>
+      </c>
+      <c r="Q36" s="8" t="n">
+        <v>2393.3</v>
       </c>
     </row>
     <row r="37">
@@ -3406,17 +3977,30 @@
       </c>
       <c r="K37" s="8" t="inlineStr">
         <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="L37" s="8" t="n">
-        <v>3089.9</v>
-      </c>
-      <c r="M37" s="8" t="n">
-        <v>589.1</v>
+          <t>HORS_PERIMETRE</t>
+        </is>
+      </c>
+      <c r="L37" s="12" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M37" s="8" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
       </c>
       <c r="N37" s="8" t="n">
-        <v>2153.1</v>
+        <v>3048.4</v>
+      </c>
+      <c r="O37" s="8" t="n">
+        <v>567.9</v>
+      </c>
+      <c r="P37" s="8" t="n">
+        <v>557</v>
+      </c>
+      <c r="Q37" s="8" t="n">
+        <v>2633.8</v>
       </c>
     </row>
     <row r="38">
@@ -3470,17 +4054,30 @@
       </c>
       <c r="K38" s="8" t="inlineStr">
         <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="L38" s="8" t="n">
-        <v>3001.1</v>
-      </c>
-      <c r="M38" s="8" t="n">
-        <v>523.9</v>
+          <t>HORS_PERIMETRE</t>
+        </is>
+      </c>
+      <c r="L38" s="12" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M38" s="8" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
       </c>
       <c r="N38" s="8" t="n">
-        <v>2497.2</v>
+        <v>2994.4</v>
+      </c>
+      <c r="O38" s="8" t="n">
+        <v>578.5</v>
+      </c>
+      <c r="P38" s="8" t="n">
+        <v>541.4</v>
+      </c>
+      <c r="Q38" s="8" t="n">
+        <v>2121.6</v>
       </c>
     </row>
     <row r="39">
@@ -3534,17 +4131,30 @@
       </c>
       <c r="K39" s="8" t="inlineStr">
         <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="L39" s="8" t="n">
-        <v>3376.9</v>
-      </c>
-      <c r="M39" s="8" t="n">
-        <v>648</v>
+          <t>HORS_PERIMETRE</t>
+        </is>
+      </c>
+      <c r="L39" s="12" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M39" s="8" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
       </c>
       <c r="N39" s="8" t="n">
-        <v>2186.2</v>
+        <v>3027.1</v>
+      </c>
+      <c r="O39" s="8" t="n">
+        <v>681</v>
+      </c>
+      <c r="P39" s="8" t="n">
+        <v>661.5</v>
+      </c>
+      <c r="Q39" s="8" t="n">
+        <v>3041.8</v>
       </c>
     </row>
     <row r="40">
@@ -3578,37 +4188,50 @@
       </c>
       <c r="G40" s="8" t="inlineStr">
         <is>
+          <t>HORS_PERIMETRE</t>
+        </is>
+      </c>
+      <c r="H40" s="13" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="I40" s="8" t="inlineStr">
+        <is>
+          <t>HORS_PERIMETRE</t>
+        </is>
+      </c>
+      <c r="J40" s="13" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="K40" s="8" t="inlineStr">
+        <is>
           <t>BLOQUE</t>
         </is>
       </c>
-      <c r="H40" s="12" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I40" s="8" t="inlineStr">
-        <is>
-          <t>HORS_PERIMETRE</t>
-        </is>
-      </c>
-      <c r="J40" s="13" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="K40" s="8" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="L40" s="8" t="n">
-        <v>2352.5</v>
-      </c>
-      <c r="M40" s="8" t="n">
-        <v>553.4</v>
+      <c r="L40" s="12" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M40" s="8" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
       </c>
       <c r="N40" s="8" t="n">
-        <v>3414.5</v>
+        <v>2390.2</v>
+      </c>
+      <c r="O40" s="8" t="n">
+        <v>575.1</v>
+      </c>
+      <c r="P40" s="8" t="n">
+        <v>580.2</v>
+      </c>
+      <c r="Q40" s="8" t="n">
+        <v>2526.7</v>
       </c>
     </row>
     <row r="41">
@@ -3662,17 +4285,30 @@
       </c>
       <c r="K41" s="8" t="inlineStr">
         <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="L41" s="8" t="n">
-        <v>2380.9</v>
-      </c>
-      <c r="M41" s="8" t="n">
-        <v>673.9</v>
+          <t>BLOQUE</t>
+        </is>
+      </c>
+      <c r="L41" s="12" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M41" s="8" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
       </c>
       <c r="N41" s="8" t="n">
-        <v>3041.3</v>
+        <v>2384.9</v>
+      </c>
+      <c r="O41" s="8" t="n">
+        <v>658.7</v>
+      </c>
+      <c r="P41" s="8" t="n">
+        <v>742.5</v>
+      </c>
+      <c r="Q41" s="8" t="n">
+        <v>2706</v>
       </c>
     </row>
     <row r="42">
@@ -3726,17 +4362,30 @@
       </c>
       <c r="K42" s="8" t="inlineStr">
         <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="L42" s="8" t="n">
-        <v>2407.8</v>
-      </c>
-      <c r="M42" s="8" t="n">
-        <v>584.8</v>
+          <t>HORS_PERIMETRE</t>
+        </is>
+      </c>
+      <c r="L42" s="13" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="M42" s="8" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
       </c>
       <c r="N42" s="8" t="n">
-        <v>1681.6</v>
+        <v>2391.3</v>
+      </c>
+      <c r="O42" s="8" t="n">
+        <v>582</v>
+      </c>
+      <c r="P42" s="8" t="n">
+        <v>562.3</v>
+      </c>
+      <c r="Q42" s="8" t="n">
+        <v>1846.5</v>
       </c>
     </row>
     <row r="43">
@@ -3790,17 +4439,30 @@
       </c>
       <c r="K43" s="8" t="inlineStr">
         <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="L43" s="8" t="n">
-        <v>2384.6</v>
-      </c>
-      <c r="M43" s="8" t="n">
-        <v>644.7</v>
+          <t>BLOQUE</t>
+        </is>
+      </c>
+      <c r="L43" s="12" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M43" s="8" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
       </c>
       <c r="N43" s="8" t="n">
-        <v>1961.8</v>
+        <v>2377.2</v>
+      </c>
+      <c r="O43" s="8" t="n">
+        <v>577.5</v>
+      </c>
+      <c r="P43" s="8" t="n">
+        <v>584.9</v>
+      </c>
+      <c r="Q43" s="8" t="n">
+        <v>1883.8</v>
       </c>
     </row>
     <row r="44">
@@ -3854,17 +4516,30 @@
       </c>
       <c r="K44" s="8" t="inlineStr">
         <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="L44" s="8" t="n">
-        <v>2396.8</v>
-      </c>
-      <c r="M44" s="8" t="n">
-        <v>554.5</v>
+          <t>HORS_PERIMETRE</t>
+        </is>
+      </c>
+      <c r="L44" s="13" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="M44" s="8" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
       </c>
       <c r="N44" s="8" t="n">
-        <v>2763.9</v>
+        <v>2369.8</v>
+      </c>
+      <c r="O44" s="8" t="n">
+        <v>573.6</v>
+      </c>
+      <c r="P44" s="8" t="n">
+        <v>569.6</v>
+      </c>
+      <c r="Q44" s="8" t="n">
+        <v>2790.2</v>
       </c>
     </row>
     <row r="45">
@@ -3898,37 +4573,50 @@
       </c>
       <c r="G45" s="8" t="inlineStr">
         <is>
+          <t>PARAMS_REQUIS</t>
+        </is>
+      </c>
+      <c r="H45" s="8" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="I45" s="8" t="inlineStr">
+        <is>
           <t>HORS_PERIMETRE</t>
         </is>
       </c>
-      <c r="H45" s="8" t="inlineStr">
+      <c r="J45" s="8" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="I45" s="8" t="inlineStr">
+      <c r="K45" s="8" t="inlineStr">
         <is>
           <t>HORS_PERIMETRE</t>
         </is>
       </c>
-      <c r="J45" s="8" t="inlineStr">
+      <c r="L45" s="8" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="K45" s="8" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="L45" s="8" t="n">
-        <v>2055.2</v>
-      </c>
-      <c r="M45" s="8" t="n">
-        <v>574.1</v>
+      <c r="M45" s="8" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
       </c>
       <c r="N45" s="8" t="n">
-        <v>1970.5</v>
+        <v>2032.6</v>
+      </c>
+      <c r="O45" s="8" t="n">
+        <v>649.5</v>
+      </c>
+      <c r="P45" s="8" t="n">
+        <v>589.4</v>
+      </c>
+      <c r="Q45" s="8" t="n">
+        <v>2935.1</v>
       </c>
     </row>
     <row r="46">
@@ -3982,17 +4670,30 @@
       </c>
       <c r="K46" s="8" t="inlineStr">
         <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="L46" s="8" t="n">
-        <v>2067.8</v>
-      </c>
-      <c r="M46" s="8" t="n">
-        <v>535.6</v>
+          <t>HORS_PERIMETRE</t>
+        </is>
+      </c>
+      <c r="L46" s="8" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="M46" s="8" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
       </c>
       <c r="N46" s="8" t="n">
-        <v>2035.1</v>
+        <v>2068.2</v>
+      </c>
+      <c r="O46" s="8" t="n">
+        <v>663.3</v>
+      </c>
+      <c r="P46" s="8" t="n">
+        <v>610.7</v>
+      </c>
+      <c r="Q46" s="8" t="n">
+        <v>2526.1</v>
       </c>
     </row>
     <row r="47">
@@ -4046,17 +4747,30 @@
       </c>
       <c r="K47" s="8" t="inlineStr">
         <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="L47" s="8" t="n">
-        <v>2057.4</v>
-      </c>
-      <c r="M47" s="8" t="n">
-        <v>544.1</v>
+          <t>HORS_PERIMETRE</t>
+        </is>
+      </c>
+      <c r="L47" s="8" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="M47" s="8" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
       </c>
       <c r="N47" s="8" t="n">
-        <v>2006.1</v>
+        <v>2051</v>
+      </c>
+      <c r="O47" s="8" t="n">
+        <v>605.9</v>
+      </c>
+      <c r="P47" s="8" t="n">
+        <v>501.1</v>
+      </c>
+      <c r="Q47" s="8" t="n">
+        <v>2414.1</v>
       </c>
     </row>
     <row r="48">
@@ -4110,17 +4824,30 @@
       </c>
       <c r="K48" s="8" t="inlineStr">
         <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="L48" s="8" t="n">
-        <v>2049.4</v>
-      </c>
-      <c r="M48" s="8" t="n">
-        <v>619.7</v>
+          <t>HORS_PERIMETRE</t>
+        </is>
+      </c>
+      <c r="L48" s="8" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="M48" s="8" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
       </c>
       <c r="N48" s="8" t="n">
-        <v>1940.7</v>
+        <v>2047.8</v>
+      </c>
+      <c r="O48" s="8" t="n">
+        <v>642.7</v>
+      </c>
+      <c r="P48" s="8" t="n">
+        <v>616.2</v>
+      </c>
+      <c r="Q48" s="8" t="n">
+        <v>2476.1</v>
       </c>
     </row>
     <row r="49">
@@ -4174,17 +4901,30 @@
       </c>
       <c r="K49" s="8" t="inlineStr">
         <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="L49" s="8" t="n">
-        <v>2033</v>
-      </c>
-      <c r="M49" s="8" t="n">
-        <v>601.5</v>
+          <t>HORS_PERIMETRE</t>
+        </is>
+      </c>
+      <c r="L49" s="8" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="M49" s="8" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
       </c>
       <c r="N49" s="8" t="n">
-        <v>2613.5</v>
+        <v>2026.7</v>
+      </c>
+      <c r="O49" s="8" t="n">
+        <v>582.8</v>
+      </c>
+      <c r="P49" s="8" t="n">
+        <v>645.8</v>
+      </c>
+      <c r="Q49" s="8" t="n">
+        <v>2256.7</v>
       </c>
     </row>
     <row r="50">
@@ -4218,7 +4958,7 @@
       </c>
       <c r="G50" s="8" t="inlineStr">
         <is>
-          <t>VERIFICATION_REQUISE</t>
+          <t>PARAMS_REQUIS</t>
         </is>
       </c>
       <c r="H50" s="13" t="inlineStr">
@@ -4228,27 +4968,40 @@
       </c>
       <c r="I50" s="8" t="inlineStr">
         <is>
-          <t>ELIGIBLE</t>
-        </is>
-      </c>
-      <c r="J50" s="12" t="inlineStr">
-        <is>
-          <t>✓</t>
+          <t>PARAMS_REQUIS</t>
+        </is>
+      </c>
+      <c r="J50" s="13" t="inlineStr">
+        <is>
+          <t>✗</t>
         </is>
       </c>
       <c r="K50" s="8" t="inlineStr">
         <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="L50" s="8" t="n">
-        <v>3907.1</v>
-      </c>
-      <c r="M50" s="8" t="n">
-        <v>922.5</v>
+          <t>REFUSE</t>
+        </is>
+      </c>
+      <c r="L50" s="13" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="M50" s="8" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
       </c>
       <c r="N50" s="8" t="n">
-        <v>6286.5</v>
+        <v>3899</v>
+      </c>
+      <c r="O50" s="8" t="n">
+        <v>696.4</v>
+      </c>
+      <c r="P50" s="8" t="n">
+        <v>749.5</v>
+      </c>
+      <c r="Q50" s="8" t="n">
+        <v>11196.4</v>
       </c>
     </row>
     <row r="51">
@@ -4282,7 +5035,7 @@
       </c>
       <c r="G51" s="8" t="inlineStr">
         <is>
-          <t>VERIFICATION_REQUISE</t>
+          <t>PARAMS_REQUIS</t>
         </is>
       </c>
       <c r="H51" s="13" t="inlineStr">
@@ -4292,27 +5045,40 @@
       </c>
       <c r="I51" s="8" t="inlineStr">
         <is>
-          <t>ELIGIBLE</t>
-        </is>
-      </c>
-      <c r="J51" s="12" t="inlineStr">
-        <is>
-          <t>✓</t>
+          <t>PARAMS_REQUIS</t>
+        </is>
+      </c>
+      <c r="J51" s="13" t="inlineStr">
+        <is>
+          <t>✗</t>
         </is>
       </c>
       <c r="K51" s="8" t="inlineStr">
         <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="L51" s="8" t="n">
-        <v>2866.6</v>
-      </c>
-      <c r="M51" s="8" t="n">
-        <v>619.3</v>
+          <t>PARAMS_REQUIS</t>
+        </is>
+      </c>
+      <c r="L51" s="13" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="M51" s="8" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
       </c>
       <c r="N51" s="8" t="n">
-        <v>4727.9</v>
+        <v>3185.1</v>
+      </c>
+      <c r="O51" s="8" t="n">
+        <v>794.2</v>
+      </c>
+      <c r="P51" s="8" t="n">
+        <v>782.6</v>
+      </c>
+      <c r="Q51" s="8" t="n">
+        <v>7479.5</v>
       </c>
     </row>
     <row r="52">
@@ -4346,7 +5112,7 @@
       </c>
       <c r="G52" s="8" t="inlineStr">
         <is>
-          <t>REFUSE</t>
+          <t>PARAMS_REQUIS</t>
         </is>
       </c>
       <c r="H52" s="13" t="inlineStr">
@@ -4356,7 +5122,7 @@
       </c>
       <c r="I52" s="8" t="inlineStr">
         <is>
-          <t>VERIFICATION_REQUISE</t>
+          <t>PARAMS_REQUIS</t>
         </is>
       </c>
       <c r="J52" s="13" t="inlineStr">
@@ -4366,17 +5132,30 @@
       </c>
       <c r="K52" s="8" t="inlineStr">
         <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="L52" s="8" t="n">
-        <v>5424.5</v>
-      </c>
-      <c r="M52" s="8" t="n">
-        <v>930.5</v>
+          <t>ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="L52" s="12" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M52" s="8" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
       </c>
       <c r="N52" s="8" t="n">
-        <v>4774.4</v>
+        <v>4049.6</v>
+      </c>
+      <c r="O52" s="8" t="n">
+        <v>729.5</v>
+      </c>
+      <c r="P52" s="8" t="n">
+        <v>700.1</v>
+      </c>
+      <c r="Q52" s="8" t="n">
+        <v>5574.8</v>
       </c>
     </row>
     <row r="53">
@@ -4410,7 +5189,7 @@
       </c>
       <c r="G53" s="8" t="inlineStr">
         <is>
-          <t>REFUSE</t>
+          <t>PARAMS_REQUIS</t>
         </is>
       </c>
       <c r="H53" s="13" t="inlineStr">
@@ -4420,7 +5199,7 @@
       </c>
       <c r="I53" s="8" t="inlineStr">
         <is>
-          <t>APPROUVE</t>
+          <t>PARAMS_REQUIS</t>
         </is>
       </c>
       <c r="J53" s="13" t="inlineStr">
@@ -4430,17 +5209,30 @@
       </c>
       <c r="K53" s="8" t="inlineStr">
         <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="L53" s="8" t="n">
-        <v>7050.8</v>
-      </c>
-      <c r="M53" s="8" t="n">
-        <v>815.5</v>
+          <t>PARAMS_REQUIS</t>
+        </is>
+      </c>
+      <c r="L53" s="13" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="M53" s="8" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
       </c>
       <c r="N53" s="8" t="n">
-        <v>9927.299999999999</v>
+        <v>6064.5</v>
+      </c>
+      <c r="O53" s="8" t="n">
+        <v>631.5</v>
+      </c>
+      <c r="P53" s="8" t="n">
+        <v>604.5</v>
+      </c>
+      <c r="Q53" s="8" t="n">
+        <v>6145.8</v>
       </c>
     </row>
     <row r="54">
@@ -4474,7 +5266,7 @@
       </c>
       <c r="G54" s="8" t="inlineStr">
         <is>
-          <t>VERIFICATION_REQUISE</t>
+          <t>PARAMS_REQUIS</t>
         </is>
       </c>
       <c r="H54" s="13" t="inlineStr">
@@ -4484,7 +5276,7 @@
       </c>
       <c r="I54" s="8" t="inlineStr">
         <is>
-          <t>(vide)</t>
+          <t>PARAMS_REQUIS</t>
         </is>
       </c>
       <c r="J54" s="13" t="inlineStr">
@@ -4494,17 +5286,30 @@
       </c>
       <c r="K54" s="8" t="inlineStr">
         <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="L54" s="8" t="n">
-        <v>5962.2</v>
-      </c>
-      <c r="M54" s="8" t="n">
-        <v>981.3</v>
+          <t>PARAMS_REQUIS</t>
+        </is>
+      </c>
+      <c r="L54" s="13" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="M54" s="8" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
       </c>
       <c r="N54" s="8" t="n">
-        <v>300048.9</v>
+        <v>5924.1</v>
+      </c>
+      <c r="O54" s="8" t="n">
+        <v>733.2</v>
+      </c>
+      <c r="P54" s="8" t="n">
+        <v>717</v>
+      </c>
+      <c r="Q54" s="8" t="n">
+        <v>4791.6</v>
       </c>
     </row>
     <row r="55">
@@ -4538,7 +5343,7 @@
       </c>
       <c r="G55" s="8" t="inlineStr">
         <is>
-          <t>VERIFICATION_REQUISE</t>
+          <t>PARAMS_REQUIS</t>
         </is>
       </c>
       <c r="H55" s="13" t="inlineStr">
@@ -4548,7 +5353,7 @@
       </c>
       <c r="I55" s="8" t="inlineStr">
         <is>
-          <t>BLOQUE</t>
+          <t>PARAMS_REQUIS</t>
         </is>
       </c>
       <c r="J55" s="13" t="inlineStr">
@@ -4558,17 +5363,30 @@
       </c>
       <c r="K55" s="8" t="inlineStr">
         <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="L55" s="8" t="n">
-        <v>8324.6</v>
-      </c>
-      <c r="M55" s="8" t="n">
-        <v>643.7</v>
+          <t>REFUSE</t>
+        </is>
+      </c>
+      <c r="L55" s="13" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="M55" s="8" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
       </c>
       <c r="N55" s="8" t="n">
-        <v>4013.9</v>
+        <v>4040.6</v>
+      </c>
+      <c r="O55" s="8" t="n">
+        <v>688.2</v>
+      </c>
+      <c r="P55" s="8" t="n">
+        <v>749.1</v>
+      </c>
+      <c r="Q55" s="8" t="n">
+        <v>5347.2</v>
       </c>
     </row>
     <row r="56">
@@ -4602,7 +5420,7 @@
       </c>
       <c r="G56" s="8" t="inlineStr">
         <is>
-          <t>VERIFICATION_REQUISE</t>
+          <t>PARAMS_REQUIS</t>
         </is>
       </c>
       <c r="H56" s="13" t="inlineStr">
@@ -4612,27 +5430,40 @@
       </c>
       <c r="I56" s="8" t="inlineStr">
         <is>
-          <t>ELIGIBLE</t>
-        </is>
-      </c>
-      <c r="J56" s="12" t="inlineStr">
-        <is>
-          <t>✓</t>
+          <t>PARAMS_REQUIS</t>
+        </is>
+      </c>
+      <c r="J56" s="13" t="inlineStr">
+        <is>
+          <t>✗</t>
         </is>
       </c>
       <c r="K56" s="8" t="inlineStr">
         <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="L56" s="8" t="n">
-        <v>4333.8</v>
-      </c>
-      <c r="M56" s="8" t="n">
-        <v>618.1</v>
+          <t>PARAMS_REQUIS</t>
+        </is>
+      </c>
+      <c r="L56" s="13" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="M56" s="8" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
       </c>
       <c r="N56" s="8" t="n">
-        <v>2721.7</v>
+        <v>4291</v>
+      </c>
+      <c r="O56" s="8" t="n">
+        <v>719.9</v>
+      </c>
+      <c r="P56" s="8" t="n">
+        <v>713.8</v>
+      </c>
+      <c r="Q56" s="8" t="n">
+        <v>4859.5</v>
       </c>
     </row>
     <row r="57">
@@ -4666,37 +5497,50 @@
       </c>
       <c r="G57" s="8" t="inlineStr">
         <is>
-          <t>REFUSE</t>
-        </is>
-      </c>
-      <c r="H57" s="12" t="inlineStr">
-        <is>
-          <t>✓</t>
+          <t>PARAMS_REQUIS</t>
+        </is>
+      </c>
+      <c r="H57" s="13" t="inlineStr">
+        <is>
+          <t>✗</t>
         </is>
       </c>
       <c r="I57" s="8" t="inlineStr">
         <is>
-          <t>REFUSE</t>
-        </is>
-      </c>
-      <c r="J57" s="12" t="inlineStr">
-        <is>
-          <t>✓</t>
+          <t>PARAMS_REQUIS</t>
+        </is>
+      </c>
+      <c r="J57" s="13" t="inlineStr">
+        <is>
+          <t>✗</t>
         </is>
       </c>
       <c r="K57" s="8" t="inlineStr">
         <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="L57" s="8" t="n">
-        <v>7538.9</v>
-      </c>
-      <c r="M57" s="8" t="n">
-        <v>701.4</v>
+          <t>PARAMS_REQUIS</t>
+        </is>
+      </c>
+      <c r="L57" s="13" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="M57" s="8" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
       </c>
       <c r="N57" s="8" t="n">
-        <v>3688.4</v>
+        <v>7225.3</v>
+      </c>
+      <c r="O57" s="8" t="n">
+        <v>764</v>
+      </c>
+      <c r="P57" s="8" t="n">
+        <v>712.5</v>
+      </c>
+      <c r="Q57" s="8" t="n">
+        <v>3059.6</v>
       </c>
     </row>
     <row r="58">
@@ -4730,37 +5574,50 @@
       </c>
       <c r="G58" s="8" t="inlineStr">
         <is>
+          <t>PARAMS_REQUIS</t>
+        </is>
+      </c>
+      <c r="H58" s="13" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="I58" s="8" t="inlineStr">
+        <is>
+          <t>PARAMS_REQUIS</t>
+        </is>
+      </c>
+      <c r="J58" s="13" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="K58" s="8" t="inlineStr">
+        <is>
           <t>ELIGIBLE</t>
         </is>
       </c>
-      <c r="H58" s="12" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I58" s="8" t="inlineStr">
-        <is>
-          <t>ELIGIBLE</t>
-        </is>
-      </c>
-      <c r="J58" s="12" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="K58" s="8" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="L58" s="8" t="n">
-        <v>6469.2</v>
-      </c>
-      <c r="M58" s="8" t="n">
-        <v>839.2</v>
+      <c r="L58" s="12" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M58" s="8" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
       </c>
       <c r="N58" s="8" t="n">
-        <v>3264.6</v>
+        <v>7495.7</v>
+      </c>
+      <c r="O58" s="8" t="n">
+        <v>590.9</v>
+      </c>
+      <c r="P58" s="8" t="n">
+        <v>650.7</v>
+      </c>
+      <c r="Q58" s="8" t="n">
+        <v>6869.4</v>
       </c>
     </row>
     <row r="59">
@@ -4814,17 +5671,30 @@
       </c>
       <c r="K59" s="8" t="inlineStr">
         <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="L59" s="8" t="n">
-        <v>7331.1</v>
-      </c>
-      <c r="M59" s="8" t="n">
-        <v>1065.5</v>
+          <t>REFUSE</t>
+        </is>
+      </c>
+      <c r="L59" s="12" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M59" s="8" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
       </c>
       <c r="N59" s="8" t="n">
-        <v>2631.5</v>
+        <v>7580</v>
+      </c>
+      <c r="O59" s="8" t="n">
+        <v>1125.7</v>
+      </c>
+      <c r="P59" s="8" t="n">
+        <v>1072.9</v>
+      </c>
+      <c r="Q59" s="8" t="n">
+        <v>3352.8</v>
       </c>
     </row>
     <row r="60">
@@ -4878,17 +5748,30 @@
       </c>
       <c r="K60" s="8" t="inlineStr">
         <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="L60" s="8" t="n">
-        <v>11542.7</v>
-      </c>
-      <c r="M60" s="8" t="n">
-        <v>683</v>
+          <t>VERIFICATION_REQUISE</t>
+        </is>
+      </c>
+      <c r="L60" s="12" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M60" s="8" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
       </c>
       <c r="N60" s="8" t="n">
-        <v>3310.5</v>
+        <v>6329.2</v>
+      </c>
+      <c r="O60" s="8" t="n">
+        <v>717.5</v>
+      </c>
+      <c r="P60" s="8" t="n">
+        <v>676.7</v>
+      </c>
+      <c r="Q60" s="8" t="n">
+        <v>5212.1</v>
       </c>
     </row>
     <row r="61">
@@ -4922,37 +5805,2052 @@
       </c>
       <c r="G61" s="8" t="inlineStr">
         <is>
+          <t>PARAMS_REQUIS</t>
+        </is>
+      </c>
+      <c r="H61" s="13" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="I61" s="8" t="inlineStr">
+        <is>
+          <t>PARAMS_REQUIS</t>
+        </is>
+      </c>
+      <c r="J61" s="13" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="K61" s="8" t="inlineStr">
+        <is>
+          <t>PARAMS_REQUIS</t>
+        </is>
+      </c>
+      <c r="L61" s="13" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="M61" s="8" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="N61" s="8" t="n">
+        <v>7116.8</v>
+      </c>
+      <c r="O61" s="8" t="n">
+        <v>741.4</v>
+      </c>
+      <c r="P61" s="8" t="n">
+        <v>720.1</v>
+      </c>
+      <c r="Q61" s="8" t="n">
+        <v>7462.8</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="8" t="inlineStr">
+        <is>
+          <t>T61</t>
+        </is>
+      </c>
+      <c r="B62" s="7" t="inlineStr">
+        <is>
+          <t>piege_endettement</t>
+        </is>
+      </c>
+      <c r="C62" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D62" s="8" t="inlineStr">
+        <is>
           <t>REFUSE</t>
         </is>
       </c>
-      <c r="H61" s="12" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I61" s="8" t="inlineStr">
+      <c r="E62" s="8" t="inlineStr">
         <is>
           <t>REFUSE</t>
         </is>
       </c>
-      <c r="J61" s="12" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="K61" s="8" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="L61" s="8" t="n">
-        <v>7420.1</v>
-      </c>
-      <c r="M61" s="8" t="n">
-        <v>1595.3</v>
-      </c>
-      <c r="N61" s="8" t="n">
-        <v>4443.8</v>
+      <c r="F62" s="12" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G62" s="8" t="inlineStr">
+        <is>
+          <t>PARAMS_REQUIS</t>
+        </is>
+      </c>
+      <c r="H62" s="13" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="I62" s="8" t="inlineStr">
+        <is>
+          <t>PARAMS_REQUIS</t>
+        </is>
+      </c>
+      <c r="J62" s="13" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="K62" s="8" t="inlineStr">
+        <is>
+          <t>REFUSE</t>
+        </is>
+      </c>
+      <c r="L62" s="12" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M62" s="8" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="N62" s="8" t="n">
+        <v>9572.6</v>
+      </c>
+      <c r="O62" s="8" t="n">
+        <v>750.7</v>
+      </c>
+      <c r="P62" s="8" t="n">
+        <v>700</v>
+      </c>
+      <c r="Q62" s="8" t="n">
+        <v>7245</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="8" t="inlineStr">
+        <is>
+          <t>T62</t>
+        </is>
+      </c>
+      <c r="B63" s="7" t="inlineStr">
+        <is>
+          <t>piege_endettement</t>
+        </is>
+      </c>
+      <c r="C63" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D63" s="8" t="inlineStr">
+        <is>
+          <t>REFUSE</t>
+        </is>
+      </c>
+      <c r="E63" s="8" t="inlineStr">
+        <is>
+          <t>REFUSE</t>
+        </is>
+      </c>
+      <c r="F63" s="12" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G63" s="8" t="inlineStr">
+        <is>
+          <t>PARAMS_REQUIS</t>
+        </is>
+      </c>
+      <c r="H63" s="13" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="I63" s="8" t="inlineStr">
+        <is>
+          <t>PARAMS_REQUIS</t>
+        </is>
+      </c>
+      <c r="J63" s="13" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="K63" s="8" t="inlineStr">
+        <is>
+          <t>PARAMS_REQUIS</t>
+        </is>
+      </c>
+      <c r="L63" s="13" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="M63" s="8" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="N63" s="8" t="n">
+        <v>8392.200000000001</v>
+      </c>
+      <c r="O63" s="8" t="n">
+        <v>712.1</v>
+      </c>
+      <c r="P63" s="8" t="n">
+        <v>727.6</v>
+      </c>
+      <c r="Q63" s="8" t="n">
+        <v>3655.3</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="8" t="inlineStr">
+        <is>
+          <t>T63</t>
+        </is>
+      </c>
+      <c r="B64" s="7" t="inlineStr">
+        <is>
+          <t>limite</t>
+        </is>
+      </c>
+      <c r="C64" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D64" s="8" t="inlineStr">
+        <is>
+          <t>ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="E64" s="8" t="inlineStr">
+        <is>
+          <t>ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="F64" s="12" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G64" s="8" t="inlineStr">
+        <is>
+          <t>PARAMS_REQUIS</t>
+        </is>
+      </c>
+      <c r="H64" s="13" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="I64" s="8" t="inlineStr">
+        <is>
+          <t>PARAMS_REQUIS</t>
+        </is>
+      </c>
+      <c r="J64" s="13" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="K64" s="8" t="inlineStr">
+        <is>
+          <t>PARAMS_REQUIS</t>
+        </is>
+      </c>
+      <c r="L64" s="13" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="M64" s="8" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="N64" s="8" t="n">
+        <v>6959.4</v>
+      </c>
+      <c r="O64" s="8" t="n">
+        <v>727.4</v>
+      </c>
+      <c r="P64" s="8" t="n">
+        <v>708.3</v>
+      </c>
+      <c r="Q64" s="8" t="n">
+        <v>7828.9</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="8" t="inlineStr">
+        <is>
+          <t>T64</t>
+        </is>
+      </c>
+      <c r="B65" s="7" t="inlineStr">
+        <is>
+          <t>piege_reorientation</t>
+        </is>
+      </c>
+      <c r="C65" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D65" s="8" t="inlineStr">
+        <is>
+          <t>REFUSE</t>
+        </is>
+      </c>
+      <c r="E65" s="8" t="inlineStr">
+        <is>
+          <t>REFUSE</t>
+        </is>
+      </c>
+      <c r="F65" s="12" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G65" s="8" t="inlineStr">
+        <is>
+          <t>PARAMS_REQUIS</t>
+        </is>
+      </c>
+      <c r="H65" s="13" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="I65" s="8" t="inlineStr">
+        <is>
+          <t>PARAMS_REQUIS</t>
+        </is>
+      </c>
+      <c r="J65" s="13" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="K65" s="8" t="inlineStr">
+        <is>
+          <t>PARAMS_REQUIS</t>
+        </is>
+      </c>
+      <c r="L65" s="13" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="M65" s="8" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="N65" s="8" t="n">
+        <v>10520.4</v>
+      </c>
+      <c r="O65" s="8" t="n">
+        <v>671.8</v>
+      </c>
+      <c r="P65" s="8" t="n">
+        <v>594</v>
+      </c>
+      <c r="Q65" s="8" t="n">
+        <v>5268.2</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="8" t="inlineStr">
+        <is>
+          <t>T65</t>
+        </is>
+      </c>
+      <c r="B66" s="7" t="inlineStr">
+        <is>
+          <t>limite</t>
+        </is>
+      </c>
+      <c r="C66" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D66" s="8" t="inlineStr">
+        <is>
+          <t>ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="E66" s="8" t="inlineStr">
+        <is>
+          <t>ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="F66" s="12" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G66" s="8" t="inlineStr">
+        <is>
+          <t>PARAMS_REQUIS</t>
+        </is>
+      </c>
+      <c r="H66" s="13" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="I66" s="8" t="inlineStr">
+        <is>
+          <t>PARAMS_REQUIS</t>
+        </is>
+      </c>
+      <c r="J66" s="13" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="K66" s="8" t="inlineStr">
+        <is>
+          <t>PARAMS_REQUIS</t>
+        </is>
+      </c>
+      <c r="L66" s="13" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="M66" s="8" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="N66" s="8" t="n">
+        <v>6938.3</v>
+      </c>
+      <c r="O66" s="8" t="n">
+        <v>739.1</v>
+      </c>
+      <c r="P66" s="8" t="n">
+        <v>720.6</v>
+      </c>
+      <c r="Q66" s="8" t="n">
+        <v>6531</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="8" t="inlineStr">
+        <is>
+          <t>T66</t>
+        </is>
+      </c>
+      <c r="B67" s="7" t="inlineStr">
+        <is>
+          <t>piege_endettement</t>
+        </is>
+      </c>
+      <c r="C67" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D67" s="8" t="inlineStr">
+        <is>
+          <t>REFUSE</t>
+        </is>
+      </c>
+      <c r="E67" s="8" t="inlineStr">
+        <is>
+          <t>REFUSE</t>
+        </is>
+      </c>
+      <c r="F67" s="12" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G67" s="8" t="inlineStr">
+        <is>
+          <t>PARAMS_REQUIS</t>
+        </is>
+      </c>
+      <c r="H67" s="13" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="I67" s="8" t="inlineStr">
+        <is>
+          <t>PARAMS_REQUIS</t>
+        </is>
+      </c>
+      <c r="J67" s="13" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="K67" s="8" t="inlineStr">
+        <is>
+          <t>ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="L67" s="13" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="M67" s="8" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="N67" s="8" t="n">
+        <v>10313.4</v>
+      </c>
+      <c r="O67" s="8" t="n">
+        <v>749.2</v>
+      </c>
+      <c r="P67" s="8" t="n">
+        <v>714</v>
+      </c>
+      <c r="Q67" s="8" t="n">
+        <v>4986.2</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="8" t="inlineStr">
+        <is>
+          <t>T67</t>
+        </is>
+      </c>
+      <c r="B68" s="7" t="inlineStr">
+        <is>
+          <t>limite</t>
+        </is>
+      </c>
+      <c r="C68" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D68" s="8" t="inlineStr">
+        <is>
+          <t>ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="E68" s="8" t="inlineStr">
+        <is>
+          <t>ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="F68" s="12" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G68" s="8" t="inlineStr">
+        <is>
+          <t>PARAMS_REQUIS</t>
+        </is>
+      </c>
+      <c r="H68" s="13" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="I68" s="8" t="inlineStr">
+        <is>
+          <t>PARAMS_REQUIS</t>
+        </is>
+      </c>
+      <c r="J68" s="13" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="K68" s="8" t="inlineStr">
+        <is>
+          <t>PARAMS_REQUIS</t>
+        </is>
+      </c>
+      <c r="L68" s="13" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="M68" s="8" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="N68" s="8" t="n">
+        <v>7189.6</v>
+      </c>
+      <c r="O68" s="8" t="n">
+        <v>753.3</v>
+      </c>
+      <c r="P68" s="8" t="n">
+        <v>749.6</v>
+      </c>
+      <c r="Q68" s="8" t="n">
+        <v>2797.2</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="8" t="inlineStr">
+        <is>
+          <t>T68</t>
+        </is>
+      </c>
+      <c r="B69" s="7" t="inlineStr">
+        <is>
+          <t>piege_endettement</t>
+        </is>
+      </c>
+      <c r="C69" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D69" s="8" t="inlineStr">
+        <is>
+          <t>REFUSE</t>
+        </is>
+      </c>
+      <c r="E69" s="8" t="inlineStr">
+        <is>
+          <t>REFUSE</t>
+        </is>
+      </c>
+      <c r="F69" s="12" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G69" s="8" t="inlineStr">
+        <is>
+          <t>REFUSE</t>
+        </is>
+      </c>
+      <c r="H69" s="12" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I69" s="8" t="inlineStr">
+        <is>
+          <t>REFUSE</t>
+        </is>
+      </c>
+      <c r="J69" s="12" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K69" s="8" t="inlineStr">
+        <is>
+          <t>PARAMS_REQUIS</t>
+        </is>
+      </c>
+      <c r="L69" s="13" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="M69" s="8" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="N69" s="8" t="n">
+        <v>7262.4</v>
+      </c>
+      <c r="O69" s="8" t="n">
+        <v>983.6</v>
+      </c>
+      <c r="P69" s="8" t="n">
+        <v>781.1</v>
+      </c>
+      <c r="Q69" s="8" t="n">
+        <v>3849.7</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="8" t="inlineStr">
+        <is>
+          <t>T69</t>
+        </is>
+      </c>
+      <c r="B70" s="7" t="inlineStr">
+        <is>
+          <t>limite</t>
+        </is>
+      </c>
+      <c r="C70" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D70" s="8" t="inlineStr">
+        <is>
+          <t>ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="E70" s="8" t="inlineStr">
+        <is>
+          <t>ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="F70" s="12" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G70" s="8" t="inlineStr">
+        <is>
+          <t>REFUSE</t>
+        </is>
+      </c>
+      <c r="H70" s="13" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="I70" s="8" t="inlineStr">
+        <is>
+          <t>REFUSE</t>
+        </is>
+      </c>
+      <c r="J70" s="13" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="K70" s="8" t="inlineStr">
+        <is>
+          <t>REFUSE</t>
+        </is>
+      </c>
+      <c r="L70" s="13" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="M70" s="8" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="N70" s="8" t="n">
+        <v>6205.3</v>
+      </c>
+      <c r="O70" s="8" t="n">
+        <v>776.5</v>
+      </c>
+      <c r="P70" s="8" t="n">
+        <v>730.7</v>
+      </c>
+      <c r="Q70" s="8" t="n">
+        <v>4040.8</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="8" t="inlineStr">
+        <is>
+          <t>T70</t>
+        </is>
+      </c>
+      <c r="B71" s="7" t="inlineStr">
+        <is>
+          <t>piege_endettement</t>
+        </is>
+      </c>
+      <c r="C71" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D71" s="8" t="inlineStr">
+        <is>
+          <t>REFUSE</t>
+        </is>
+      </c>
+      <c r="E71" s="8" t="inlineStr">
+        <is>
+          <t>REFUSE</t>
+        </is>
+      </c>
+      <c r="F71" s="12" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G71" s="8" t="inlineStr">
+        <is>
+          <t>REFUSE</t>
+        </is>
+      </c>
+      <c r="H71" s="12" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I71" s="8" t="inlineStr">
+        <is>
+          <t>REFUSE</t>
+        </is>
+      </c>
+      <c r="J71" s="12" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K71" s="8" t="inlineStr">
+        <is>
+          <t>REFUSE</t>
+        </is>
+      </c>
+      <c r="L71" s="12" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M71" s="8" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="N71" s="8" t="n">
+        <v>8744.299999999999</v>
+      </c>
+      <c r="O71" s="8" t="n">
+        <v>924.1</v>
+      </c>
+      <c r="P71" s="8" t="n">
+        <v>957.8</v>
+      </c>
+      <c r="Q71" s="8" t="n">
+        <v>5825.6</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="8" t="inlineStr">
+        <is>
+          <t>T71</t>
+        </is>
+      </c>
+      <c r="B72" s="7" t="inlineStr">
+        <is>
+          <t>limite</t>
+        </is>
+      </c>
+      <c r="C72" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D72" s="8" t="inlineStr">
+        <is>
+          <t>REFUSE</t>
+        </is>
+      </c>
+      <c r="E72" s="8" t="inlineStr">
+        <is>
+          <t>REFUSE</t>
+        </is>
+      </c>
+      <c r="F72" s="12" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G72" s="8" t="inlineStr">
+        <is>
+          <t>PARAMS_REQUIS</t>
+        </is>
+      </c>
+      <c r="H72" s="13" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="I72" s="8" t="inlineStr">
+        <is>
+          <t>PARAMS_REQUIS</t>
+        </is>
+      </c>
+      <c r="J72" s="13" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="K72" s="8" t="inlineStr">
+        <is>
+          <t>PARAMS_REQUIS</t>
+        </is>
+      </c>
+      <c r="L72" s="13" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="M72" s="8" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="N72" s="8" t="n">
+        <v>6321.5</v>
+      </c>
+      <c r="O72" s="8" t="n">
+        <v>692.3</v>
+      </c>
+      <c r="P72" s="8" t="n">
+        <v>710.3</v>
+      </c>
+      <c r="Q72" s="8" t="n">
+        <v>3371.8</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="8" t="inlineStr">
+        <is>
+          <t>T72</t>
+        </is>
+      </c>
+      <c r="B73" s="7" t="inlineStr">
+        <is>
+          <t>piege_endettement</t>
+        </is>
+      </c>
+      <c r="C73" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D73" s="8" t="inlineStr">
+        <is>
+          <t>REFUSE</t>
+        </is>
+      </c>
+      <c r="E73" s="8" t="inlineStr">
+        <is>
+          <t>REFUSE</t>
+        </is>
+      </c>
+      <c r="F73" s="12" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G73" s="8" t="inlineStr">
+        <is>
+          <t>REFUSE</t>
+        </is>
+      </c>
+      <c r="H73" s="12" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I73" s="8" t="inlineStr">
+        <is>
+          <t>HORS_PERIMETRE</t>
+        </is>
+      </c>
+      <c r="J73" s="13" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="K73" s="8" t="inlineStr">
+        <is>
+          <t>REFUSE</t>
+        </is>
+      </c>
+      <c r="L73" s="12" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M73" s="8" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="N73" s="8" t="n">
+        <v>5768.7</v>
+      </c>
+      <c r="O73" s="8" t="n">
+        <v>689.9</v>
+      </c>
+      <c r="P73" s="8" t="n">
+        <v>683.1</v>
+      </c>
+      <c r="Q73" s="8" t="n">
+        <v>3100.2</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="8" t="inlineStr">
+        <is>
+          <t>T73</t>
+        </is>
+      </c>
+      <c r="B74" s="7" t="inlineStr">
+        <is>
+          <t>params_manquants</t>
+        </is>
+      </c>
+      <c r="C74" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D74" s="8" t="inlineStr">
+        <is>
+          <t>PARAMS_REQUIS</t>
+        </is>
+      </c>
+      <c r="E74" s="8" t="inlineStr">
+        <is>
+          <t>PARAMS_REQUIS</t>
+        </is>
+      </c>
+      <c r="F74" s="12" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G74" s="8" t="inlineStr">
+        <is>
+          <t>PARAMS_REQUIS</t>
+        </is>
+      </c>
+      <c r="H74" s="12" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I74" s="8" t="inlineStr">
+        <is>
+          <t>PARAMS_REQUIS</t>
+        </is>
+      </c>
+      <c r="J74" s="12" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K74" s="8" t="inlineStr">
+        <is>
+          <t>PARAMS_REQUIS</t>
+        </is>
+      </c>
+      <c r="L74" s="12" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M74" s="8" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="N74" s="8" t="n">
+        <v>2923.8</v>
+      </c>
+      <c r="O74" s="8" t="n">
+        <v>693.6</v>
+      </c>
+      <c r="P74" s="8" t="n">
+        <v>629.4</v>
+      </c>
+      <c r="Q74" s="8" t="n">
+        <v>2174.6</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="8" t="inlineStr">
+        <is>
+          <t>T74</t>
+        </is>
+      </c>
+      <c r="B75" s="7" t="inlineStr">
+        <is>
+          <t>limite</t>
+        </is>
+      </c>
+      <c r="C75" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D75" s="8" t="inlineStr">
+        <is>
+          <t>APPROUVE</t>
+        </is>
+      </c>
+      <c r="E75" s="8" t="inlineStr">
+        <is>
+          <t>APPROUVE</t>
+        </is>
+      </c>
+      <c r="F75" s="12" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G75" s="8" t="inlineStr">
+        <is>
+          <t>PARAMS_REQUIS</t>
+        </is>
+      </c>
+      <c r="H75" s="13" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="I75" s="8" t="inlineStr">
+        <is>
+          <t>PARAMS_REQUIS</t>
+        </is>
+      </c>
+      <c r="J75" s="13" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="K75" s="8" t="inlineStr">
+        <is>
+          <t>PARAMS_REQUIS</t>
+        </is>
+      </c>
+      <c r="L75" s="13" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="M75" s="8" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="N75" s="8" t="n">
+        <v>5848.7</v>
+      </c>
+      <c r="O75" s="8" t="n">
+        <v>669.8</v>
+      </c>
+      <c r="P75" s="8" t="n">
+        <v>739.4</v>
+      </c>
+      <c r="Q75" s="8" t="n">
+        <v>1916.9</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="8" t="inlineStr">
+        <is>
+          <t>T75</t>
+        </is>
+      </c>
+      <c r="B76" s="7" t="inlineStr">
+        <is>
+          <t>limite</t>
+        </is>
+      </c>
+      <c r="C76" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D76" s="8" t="inlineStr">
+        <is>
+          <t>VERIFICATION_REQUISE</t>
+        </is>
+      </c>
+      <c r="E76" s="8" t="inlineStr">
+        <is>
+          <t>VERIFICATION_REQUISE</t>
+        </is>
+      </c>
+      <c r="F76" s="12" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G76" s="8" t="inlineStr">
+        <is>
+          <t>PARAMS_REQUIS</t>
+        </is>
+      </c>
+      <c r="H76" s="13" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="I76" s="8" t="inlineStr">
+        <is>
+          <t>PARAMS_REQUIS</t>
+        </is>
+      </c>
+      <c r="J76" s="13" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="K76" s="8" t="inlineStr">
+        <is>
+          <t>PARAMS_REQUIS</t>
+        </is>
+      </c>
+      <c r="L76" s="13" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="M76" s="8" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="N76" s="8" t="n">
+        <v>5302.9</v>
+      </c>
+      <c r="O76" s="8" t="n">
+        <v>667.3</v>
+      </c>
+      <c r="P76" s="8" t="n">
+        <v>964.6</v>
+      </c>
+      <c r="Q76" s="8" t="n">
+        <v>2818.3</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="8" t="inlineStr">
+        <is>
+          <t>T76</t>
+        </is>
+      </c>
+      <c r="B77" s="7" t="inlineStr">
+        <is>
+          <t>params_manquants</t>
+        </is>
+      </c>
+      <c r="C77" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D77" s="8" t="inlineStr">
+        <is>
+          <t>PARAMS_REQUIS</t>
+        </is>
+      </c>
+      <c r="E77" s="8" t="inlineStr">
+        <is>
+          <t>PARAMS_REQUIS</t>
+        </is>
+      </c>
+      <c r="F77" s="12" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G77" s="8" t="inlineStr">
+        <is>
+          <t>PARAMS_REQUIS</t>
+        </is>
+      </c>
+      <c r="H77" s="12" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I77" s="8" t="inlineStr">
+        <is>
+          <t>PARAMS_REQUIS</t>
+        </is>
+      </c>
+      <c r="J77" s="12" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K77" s="8" t="inlineStr">
+        <is>
+          <t>PARAMS_REQUIS</t>
+        </is>
+      </c>
+      <c r="L77" s="12" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M77" s="8" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="N77" s="8" t="n">
+        <v>3933.7</v>
+      </c>
+      <c r="O77" s="8" t="n">
+        <v>860.5</v>
+      </c>
+      <c r="P77" s="8" t="n">
+        <v>828.8</v>
+      </c>
+      <c r="Q77" s="8" t="n">
+        <v>4877.7</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="8" t="inlineStr">
+        <is>
+          <t>T77</t>
+        </is>
+      </c>
+      <c r="B78" s="7" t="inlineStr">
+        <is>
+          <t>params_manquants</t>
+        </is>
+      </c>
+      <c r="C78" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D78" s="8" t="inlineStr">
+        <is>
+          <t>PARAMS_REQUIS</t>
+        </is>
+      </c>
+      <c r="E78" s="8" t="inlineStr">
+        <is>
+          <t>PARAMS_REQUIS</t>
+        </is>
+      </c>
+      <c r="F78" s="12" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G78" s="8" t="inlineStr">
+        <is>
+          <t>PARAMS_REQUIS</t>
+        </is>
+      </c>
+      <c r="H78" s="12" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I78" s="8" t="inlineStr">
+        <is>
+          <t>PARAMS_REQUIS</t>
+        </is>
+      </c>
+      <c r="J78" s="12" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K78" s="8" t="inlineStr">
+        <is>
+          <t>PARAMS_REQUIS</t>
+        </is>
+      </c>
+      <c r="L78" s="12" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M78" s="8" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="N78" s="8" t="n">
+        <v>3882.2</v>
+      </c>
+      <c r="O78" s="8" t="n">
+        <v>714.2</v>
+      </c>
+      <c r="P78" s="8" t="n">
+        <v>697.2</v>
+      </c>
+      <c r="Q78" s="8" t="n">
+        <v>2940.2</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="8" t="inlineStr">
+        <is>
+          <t>T78</t>
+        </is>
+      </c>
+      <c r="B79" s="7" t="inlineStr">
+        <is>
+          <t>params_manquants</t>
+        </is>
+      </c>
+      <c r="C79" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D79" s="8" t="inlineStr">
+        <is>
+          <t>PARAMS_REQUIS</t>
+        </is>
+      </c>
+      <c r="E79" s="8" t="inlineStr">
+        <is>
+          <t>PARAMS_REQUIS</t>
+        </is>
+      </c>
+      <c r="F79" s="12" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G79" s="8" t="inlineStr">
+        <is>
+          <t>PARAMS_REQUIS</t>
+        </is>
+      </c>
+      <c r="H79" s="12" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I79" s="8" t="inlineStr">
+        <is>
+          <t>PARAMS_REQUIS</t>
+        </is>
+      </c>
+      <c r="J79" s="12" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K79" s="8" t="inlineStr">
+        <is>
+          <t>PARAMS_REQUIS</t>
+        </is>
+      </c>
+      <c r="L79" s="12" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M79" s="8" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="N79" s="8" t="n">
+        <v>3850.9</v>
+      </c>
+      <c r="O79" s="8" t="n">
+        <v>706</v>
+      </c>
+      <c r="P79" s="8" t="n">
+        <v>704.5</v>
+      </c>
+      <c r="Q79" s="8" t="n">
+        <v>3780.3</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="8" t="inlineStr">
+        <is>
+          <t>T79</t>
+        </is>
+      </c>
+      <c r="B80" s="7" t="inlineStr">
+        <is>
+          <t>params_manquants</t>
+        </is>
+      </c>
+      <c r="C80" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D80" s="8" t="inlineStr">
+        <is>
+          <t>PARAMS_REQUIS</t>
+        </is>
+      </c>
+      <c r="E80" s="8" t="inlineStr">
+        <is>
+          <t>PARAMS_REQUIS</t>
+        </is>
+      </c>
+      <c r="F80" s="12" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G80" s="8" t="inlineStr">
+        <is>
+          <t>PARAMS_REQUIS</t>
+        </is>
+      </c>
+      <c r="H80" s="12" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I80" s="8" t="inlineStr">
+        <is>
+          <t>PARAMS_REQUIS</t>
+        </is>
+      </c>
+      <c r="J80" s="12" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K80" s="8" t="inlineStr">
+        <is>
+          <t>PARAMS_REQUIS</t>
+        </is>
+      </c>
+      <c r="L80" s="12" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M80" s="8" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="N80" s="8" t="n">
+        <v>3809</v>
+      </c>
+      <c r="O80" s="8" t="n">
+        <v>895.9</v>
+      </c>
+      <c r="P80" s="8" t="n">
+        <v>638.3</v>
+      </c>
+      <c r="Q80" s="8" t="n">
+        <v>2908.9</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="8" t="inlineStr">
+        <is>
+          <t>T80</t>
+        </is>
+      </c>
+      <c r="B81" s="7" t="inlineStr">
+        <is>
+          <t>params_manquants</t>
+        </is>
+      </c>
+      <c r="C81" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D81" s="8" t="inlineStr">
+        <is>
+          <t>PARAMS_REQUIS</t>
+        </is>
+      </c>
+      <c r="E81" s="8" t="inlineStr">
+        <is>
+          <t>PARAMS_REQUIS</t>
+        </is>
+      </c>
+      <c r="F81" s="12" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G81" s="8" t="inlineStr">
+        <is>
+          <t>PARAMS_REQUIS</t>
+        </is>
+      </c>
+      <c r="H81" s="12" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I81" s="8" t="inlineStr">
+        <is>
+          <t>PARAMS_REQUIS</t>
+        </is>
+      </c>
+      <c r="J81" s="12" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K81" s="8" t="inlineStr">
+        <is>
+          <t>PARAMS_REQUIS</t>
+        </is>
+      </c>
+      <c r="L81" s="12" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M81" s="8" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="N81" s="8" t="n">
+        <v>3831.7</v>
+      </c>
+      <c r="O81" s="8" t="n">
+        <v>633.2</v>
+      </c>
+      <c r="P81" s="8" t="n">
+        <v>631.8</v>
+      </c>
+      <c r="Q81" s="8" t="n">
+        <v>2066</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="8" t="inlineStr">
+        <is>
+          <t>T81</t>
+        </is>
+      </c>
+      <c r="B82" s="7" t="inlineStr">
+        <is>
+          <t>params_manquants</t>
+        </is>
+      </c>
+      <c r="C82" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D82" s="8" t="inlineStr">
+        <is>
+          <t>PARAMS_REQUIS</t>
+        </is>
+      </c>
+      <c r="E82" s="8" t="inlineStr">
+        <is>
+          <t>PARAMS_REQUIS</t>
+        </is>
+      </c>
+      <c r="F82" s="12" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G82" s="8" t="inlineStr">
+        <is>
+          <t>PARAMS_REQUIS</t>
+        </is>
+      </c>
+      <c r="H82" s="12" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I82" s="8" t="inlineStr">
+        <is>
+          <t>PARAMS_REQUIS</t>
+        </is>
+      </c>
+      <c r="J82" s="12" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K82" s="8" t="inlineStr">
+        <is>
+          <t>PARAMS_REQUIS</t>
+        </is>
+      </c>
+      <c r="L82" s="12" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M82" s="8" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="N82" s="8" t="n">
+        <v>3737.6</v>
+      </c>
+      <c r="O82" s="8" t="n">
+        <v>698.5</v>
+      </c>
+      <c r="P82" s="8" t="n">
+        <v>689.9</v>
+      </c>
+      <c r="Q82" s="8" t="n">
+        <v>2924.4</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="8" t="inlineStr">
+        <is>
+          <t>T82</t>
+        </is>
+      </c>
+      <c r="B83" s="7" t="inlineStr">
+        <is>
+          <t>params_manquants</t>
+        </is>
+      </c>
+      <c r="C83" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D83" s="8" t="inlineStr">
+        <is>
+          <t>PARAMS_REQUIS</t>
+        </is>
+      </c>
+      <c r="E83" s="8" t="inlineStr">
+        <is>
+          <t>PARAMS_REQUIS</t>
+        </is>
+      </c>
+      <c r="F83" s="12" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G83" s="8" t="inlineStr">
+        <is>
+          <t>PARAMS_REQUIS</t>
+        </is>
+      </c>
+      <c r="H83" s="12" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I83" s="8" t="inlineStr">
+        <is>
+          <t>PARAMS_REQUIS</t>
+        </is>
+      </c>
+      <c r="J83" s="12" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K83" s="8" t="inlineStr">
+        <is>
+          <t>PARAMS_REQUIS</t>
+        </is>
+      </c>
+      <c r="L83" s="12" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M83" s="8" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="N83" s="8" t="n">
+        <v>3848.9</v>
+      </c>
+      <c r="O83" s="8" t="n">
+        <v>614.9</v>
+      </c>
+      <c r="P83" s="8" t="n">
+        <v>580.4</v>
+      </c>
+      <c r="Q83" s="8" t="n">
+        <v>2412.8</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="8" t="inlineStr">
+        <is>
+          <t>T83</t>
+        </is>
+      </c>
+      <c r="B84" s="7" t="inlineStr">
+        <is>
+          <t>params_manquants</t>
+        </is>
+      </c>
+      <c r="C84" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D84" s="8" t="inlineStr">
+        <is>
+          <t>PARAMS_REQUIS</t>
+        </is>
+      </c>
+      <c r="E84" s="8" t="inlineStr">
+        <is>
+          <t>PARAMS_REQUIS</t>
+        </is>
+      </c>
+      <c r="F84" s="12" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G84" s="8" t="inlineStr">
+        <is>
+          <t>PARAMS_REQUIS</t>
+        </is>
+      </c>
+      <c r="H84" s="12" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I84" s="8" t="inlineStr">
+        <is>
+          <t>PARAMS_REQUIS</t>
+        </is>
+      </c>
+      <c r="J84" s="12" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K84" s="8" t="inlineStr">
+        <is>
+          <t>PARAMS_REQUIS</t>
+        </is>
+      </c>
+      <c r="L84" s="12" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M84" s="8" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="N84" s="8" t="n">
+        <v>3732.6</v>
+      </c>
+      <c r="O84" s="8" t="n">
+        <v>745.1</v>
+      </c>
+      <c r="P84" s="8" t="n">
+        <v>722.3</v>
+      </c>
+      <c r="Q84" s="8" t="n">
+        <v>1873.3</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="8" t="inlineStr">
+        <is>
+          <t>T84</t>
+        </is>
+      </c>
+      <c r="B85" s="7" t="inlineStr">
+        <is>
+          <t>params_manquants</t>
+        </is>
+      </c>
+      <c r="C85" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D85" s="8" t="inlineStr">
+        <is>
+          <t>PARAMS_REQUIS</t>
+        </is>
+      </c>
+      <c r="E85" s="8" t="inlineStr">
+        <is>
+          <t>PARAMS_REQUIS</t>
+        </is>
+      </c>
+      <c r="F85" s="12" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G85" s="8" t="inlineStr">
+        <is>
+          <t>PARAMS_REQUIS</t>
+        </is>
+      </c>
+      <c r="H85" s="12" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I85" s="8" t="inlineStr">
+        <is>
+          <t>PARAMS_REQUIS</t>
+        </is>
+      </c>
+      <c r="J85" s="12" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K85" s="8" t="inlineStr">
+        <is>
+          <t>PARAMS_REQUIS</t>
+        </is>
+      </c>
+      <c r="L85" s="12" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M85" s="8" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="N85" s="8" t="n">
+        <v>3779.3</v>
+      </c>
+      <c r="O85" s="8" t="n">
+        <v>691.3</v>
+      </c>
+      <c r="P85" s="8" t="n">
+        <v>677.1</v>
+      </c>
+      <c r="Q85" s="8" t="n">
+        <v>4723.8</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="8" t="inlineStr">
+        <is>
+          <t>T85</t>
+        </is>
+      </c>
+      <c r="B86" s="7" t="inlineStr">
+        <is>
+          <t>params_manquants</t>
+        </is>
+      </c>
+      <c r="C86" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D86" s="8" t="inlineStr">
+        <is>
+          <t>PARAMS_REQUIS</t>
+        </is>
+      </c>
+      <c r="E86" s="8" t="inlineStr">
+        <is>
+          <t>PARAMS_REQUIS</t>
+        </is>
+      </c>
+      <c r="F86" s="12" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G86" s="8" t="inlineStr">
+        <is>
+          <t>VERIFICATION_REQUISE</t>
+        </is>
+      </c>
+      <c r="H86" s="13" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="I86" s="8" t="inlineStr">
+        <is>
+          <t>VERIFICATION_REQUISE</t>
+        </is>
+      </c>
+      <c r="J86" s="13" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="K86" s="8" t="inlineStr">
+        <is>
+          <t>PARAMS_REQUIS</t>
+        </is>
+      </c>
+      <c r="L86" s="12" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M86" s="8" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="N86" s="8" t="n">
+        <v>3894.9</v>
+      </c>
+      <c r="O86" s="8" t="n">
+        <v>693.6</v>
+      </c>
+      <c r="P86" s="8" t="n">
+        <v>648.8</v>
+      </c>
+      <c r="Q86" s="8" t="n">
+        <v>2977.9</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="8" t="inlineStr">
+        <is>
+          <t>T86</t>
+        </is>
+      </c>
+      <c r="B87" s="7" t="inlineStr">
+        <is>
+          <t>params_manquants</t>
+        </is>
+      </c>
+      <c r="C87" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D87" s="8" t="inlineStr">
+        <is>
+          <t>PARAMS_REQUIS</t>
+        </is>
+      </c>
+      <c r="E87" s="8" t="inlineStr">
+        <is>
+          <t>PARAMS_REQUIS</t>
+        </is>
+      </c>
+      <c r="F87" s="12" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G87" s="8" t="inlineStr">
+        <is>
+          <t>PARAMS_REQUIS</t>
+        </is>
+      </c>
+      <c r="H87" s="12" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I87" s="8" t="inlineStr">
+        <is>
+          <t>PARAMS_REQUIS</t>
+        </is>
+      </c>
+      <c r="J87" s="12" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K87" s="8" t="inlineStr">
+        <is>
+          <t>PARAMS_REQUIS</t>
+        </is>
+      </c>
+      <c r="L87" s="12" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M87" s="8" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="N87" s="8" t="n">
+        <v>2939.2</v>
+      </c>
+      <c r="O87" s="8" t="n">
+        <v>611</v>
+      </c>
+      <c r="P87" s="8" t="n">
+        <v>559.8</v>
+      </c>
+      <c r="Q87" s="8" t="n">
+        <v>2535.2</v>
       </c>
     </row>
   </sheetData>
@@ -4966,15 +7864,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5002,15 +7901,20 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>Montant (LLM rapide)</t>
+          <t>Montant (LLM T=0)</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>Montant (LLM raisonn.)</t>
+          <t>Montant (LLM T=0.2)</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Montant (LLM T=0.2+rais.)</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>Décision attendue</t>
         </is>
@@ -5033,10 +7937,11 @@
         </is>
       </c>
       <c r="D4" s="8" t="n"/>
-      <c r="E4" s="8" t="n">
+      <c r="E4" s="8" t="n"/>
+      <c r="F4" s="8" t="n">
         <v>200000</v>
       </c>
-      <c r="F4" s="8" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
         <is>
           <t>ELIGIBLE</t>
         </is>
@@ -5045,64 +7950,66 @@
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>T02</t>
+          <t>T03</t>
         </is>
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>Crédit immo eligible revenu élevé</t>
+          <t>Crédit immo refusé taux trop élevé</t>
         </is>
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>nominal</t>
+          <t>piege_endettement</t>
         </is>
       </c>
       <c r="D5" s="8" t="n"/>
-      <c r="E5" s="8" t="n">
-        <v>300000</v>
-      </c>
-      <c r="F5" s="8" t="inlineStr">
-        <is>
-          <t>ELIGIBLE</t>
+      <c r="E5" s="8" t="n"/>
+      <c r="F5" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="8" t="inlineStr">
+        <is>
+          <t>REFUSE</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>T04</t>
+          <t>T05</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Crédit immo refusé montant trop faible</t>
+          <t>Crédit immo limite endettement 35%</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>piege_reorientation</t>
+          <t>limite</t>
         </is>
       </c>
       <c r="D6" s="8" t="n"/>
-      <c r="E6" s="8" t="n">
-        <v>10000</v>
-      </c>
-      <c r="F6" s="8" t="inlineStr">
-        <is>
-          <t>REFUSE</t>
+      <c r="E6" s="8" t="n"/>
+      <c r="F6" s="8" t="n">
+        <v>168000</v>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>ELIGIBLE</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>T07</t>
+          <t>T09</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>Crédit immo avec apport</t>
+          <t>Crédit conso eligible petit montant</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
@@ -5110,13 +8017,12 @@
           <t>nominal</t>
         </is>
       </c>
-      <c r="D7" s="8" t="n">
-        <v>150000</v>
-      </c>
-      <c r="E7" s="8" t="n">
-        <v>150000</v>
-      </c>
-      <c r="F7" s="8" t="inlineStr">
+      <c r="D7" s="8" t="n"/>
+      <c r="E7" s="8" t="n"/>
+      <c r="F7" s="8" t="n">
+        <v>3000</v>
+      </c>
+      <c r="G7" s="8" t="inlineStr">
         <is>
           <t>ELIGIBLE</t>
         </is>
@@ -5125,106 +8031,106 @@
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>T08</t>
+          <t>T11</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Crédit conso complet eligible</t>
+          <t>Crédit conso refusé au dessus plafond</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>nominal</t>
-        </is>
-      </c>
-      <c r="D8" s="8" t="n">
-        <v>8000</v>
-      </c>
-      <c r="E8" s="8" t="n">
-        <v>7500</v>
-      </c>
-      <c r="F8" s="8" t="inlineStr">
-        <is>
-          <t>ELIGIBLE</t>
+          <t>piege_reorientation</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="n"/>
+      <c r="E8" s="8" t="n"/>
+      <c r="F8" s="8" t="n">
+        <v>90000</v>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>REFUSE</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>T09</t>
+          <t>T13</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>Crédit conso eligible petit montant</t>
+          <t>Crédit conso juste au dessus plafond</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>nominal</t>
+          <t>piege_reorientation</t>
         </is>
       </c>
       <c r="D9" s="8" t="n"/>
-      <c r="E9" s="8" t="n">
-        <v>3000</v>
-      </c>
-      <c r="F9" s="8" t="inlineStr">
-        <is>
-          <t>ELIGIBLE</t>
+      <c r="E9" s="8" t="n"/>
+      <c r="F9" s="8" t="n">
+        <v>30000</v>
+      </c>
+      <c r="G9" s="8" t="inlineStr">
+        <is>
+          <t>REFUSE</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>T11</t>
+          <t>T14</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Crédit conso refusé au dessus plafond</t>
+          <t>Crédit conso voiture</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>piege_reorientation</t>
-        </is>
-      </c>
-      <c r="D10" s="8" t="n">
-        <v>90000</v>
-      </c>
-      <c r="E10" s="8" t="n">
-        <v>90000</v>
-      </c>
-      <c r="F10" s="8" t="inlineStr">
-        <is>
-          <t>REFUSE</t>
+          <t>nominal</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="n"/>
+      <c r="E10" s="8" t="n"/>
+      <c r="F10" s="8" t="n">
+        <v>15000</v>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>ELIGIBLE</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>T12</t>
+          <t>T15</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>Crédit conso pile au plafond 75000</t>
+          <t>Crédit conso travaux</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>limite</t>
+          <t>nominal</t>
         </is>
       </c>
       <c r="D11" s="8" t="n"/>
-      <c r="E11" s="8" t="n">
-        <v>75000</v>
-      </c>
-      <c r="F11" s="8" t="inlineStr">
+      <c r="E11" s="8" t="n"/>
+      <c r="F11" s="8" t="n">
+        <v>20000</v>
+      </c>
+      <c r="G11" s="8" t="inlineStr">
         <is>
           <t>ELIGIBLE</t>
         </is>
@@ -5233,50 +8139,52 @@
     <row r="12">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>T13</t>
+          <t>T49</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Crédit conso juste au dessus plafond</t>
+          <t>Multi-tour immo collecte complète</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>piege_reorientation</t>
+          <t>multitour</t>
         </is>
       </c>
       <c r="D12" s="8" t="n"/>
-      <c r="E12" s="8" t="n">
-        <v>25000</v>
-      </c>
-      <c r="F12" s="8" t="inlineStr">
-        <is>
-          <t>REFUSE</t>
+      <c r="E12" s="8" t="n"/>
+      <c r="F12" s="8" t="n">
+        <v>150000</v>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>ELIGIBLE</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>T14</t>
+          <t>T51</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Crédit conso voiture</t>
+          <t>Multi-tour conso collecte</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>nominal</t>
+          <t>multitour</t>
         </is>
       </c>
       <c r="D13" s="8" t="n"/>
-      <c r="E13" s="8" t="n">
-        <v>15000</v>
-      </c>
-      <c r="F13" s="8" t="inlineStr">
+      <c r="E13" s="8" t="n"/>
+      <c r="F13" s="8" t="n">
+        <v>10000</v>
+      </c>
+      <c r="G13" s="8" t="inlineStr">
         <is>
           <t>ELIGIBLE</t>
         </is>
@@ -5285,12 +8193,12 @@
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t>T15</t>
+          <t>T57</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Crédit conso travaux</t>
+          <t>Crédit conso limite basse montant</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -5299,10 +8207,11 @@
         </is>
       </c>
       <c r="D14" s="8" t="n"/>
-      <c r="E14" s="8" t="n">
-        <v>20000</v>
-      </c>
-      <c r="F14" s="8" t="inlineStr">
+      <c r="E14" s="8" t="n"/>
+      <c r="F14" s="8" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G14" s="8" t="inlineStr">
         <is>
           <t>ELIGIBLE</t>
         </is>
@@ -5311,216 +8220,27 @@
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>T23</t>
+          <t>T66</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Carte plafond dans limite</t>
+          <t>Crédit immo age fin 76</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>nominal</t>
-        </is>
-      </c>
-      <c r="D15" s="8" t="n">
-        <v>3000</v>
-      </c>
-      <c r="E15" s="8" t="n">
-        <v>3000</v>
-      </c>
-      <c r="F15" s="8" t="inlineStr">
-        <is>
-          <t>APPROUVE</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="8" t="inlineStr">
-        <is>
-          <t>T24</t>
-        </is>
-      </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>Carte plafond excessif</t>
-        </is>
-      </c>
-      <c r="C16" s="8" t="inlineStr">
-        <is>
-          <t>limite</t>
-        </is>
-      </c>
-      <c r="D16" s="8" t="n">
-        <v>20000</v>
-      </c>
-      <c r="E16" s="8" t="n">
-        <v>20000</v>
-      </c>
-      <c r="F16" s="8" t="inlineStr">
-        <is>
-          <t>VERIFICATION_REQUISE</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="8" t="inlineStr">
-        <is>
-          <t>T49</t>
-        </is>
-      </c>
-      <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>Multi-tour immo collecte complète</t>
-        </is>
-      </c>
-      <c r="C17" s="8" t="inlineStr">
-        <is>
-          <t>multitour</t>
-        </is>
-      </c>
-      <c r="D17" s="8" t="n"/>
-      <c r="E17" s="8" t="n">
-        <v>200000</v>
-      </c>
-      <c r="F17" s="8" t="inlineStr">
-        <is>
-          <t>ELIGIBLE</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="8" t="inlineStr">
-        <is>
-          <t>T50</t>
-        </is>
-      </c>
-      <c r="B18" s="7" t="inlineStr">
-        <is>
-          <t>Multi-tour clarification puis params</t>
-        </is>
-      </c>
-      <c r="C18" s="8" t="inlineStr">
-        <is>
-          <t>multitour</t>
-        </is>
-      </c>
-      <c r="D18" s="8" t="n">
-        <v>150000</v>
-      </c>
-      <c r="E18" s="8" t="n">
-        <v>150000</v>
-      </c>
-      <c r="F18" s="8" t="inlineStr">
-        <is>
-          <t>ELIGIBLE</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="8" t="inlineStr">
-        <is>
-          <t>T52</t>
-        </is>
-      </c>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>Multi-tour suivi durée</t>
-        </is>
-      </c>
-      <c r="C19" s="8" t="inlineStr">
-        <is>
-          <t>multitour</t>
-        </is>
-      </c>
-      <c r="D19" s="8" t="n"/>
-      <c r="E19" s="8" t="n">
-        <v>10000</v>
-      </c>
-      <c r="F19" s="8" t="inlineStr">
-        <is>
-          <t>ELIGIBLE</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="8" t="inlineStr">
-        <is>
-          <t>T54</t>
-        </is>
-      </c>
-      <c r="B20" s="7" t="inlineStr">
-        <is>
-          <t>Multi-tour changement de sujet</t>
-        </is>
-      </c>
-      <c r="C20" s="8" t="inlineStr">
-        <is>
-          <t>multitour</t>
-        </is>
-      </c>
-      <c r="D20" s="8" t="n">
-        <v>200000</v>
-      </c>
-      <c r="E20" s="8" t="n"/>
-      <c r="F20" s="8" t="inlineStr">
-        <is>
-          <t>APPROUVE</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="8" t="inlineStr">
-        <is>
-          <t>T55</t>
-        </is>
-      </c>
-      <c r="B21" s="7" t="inlineStr">
-        <is>
-          <t>Multi-tour params partiels immo</t>
-        </is>
-      </c>
-      <c r="C21" s="8" t="inlineStr">
-        <is>
-          <t>multitour</t>
-        </is>
-      </c>
-      <c r="D21" s="8" t="n"/>
-      <c r="E21" s="8" t="n">
-        <v>200000</v>
-      </c>
-      <c r="F21" s="8" t="inlineStr">
-        <is>
-          <t>ELIGIBLE</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="8" t="inlineStr">
-        <is>
-          <t>T57</t>
-        </is>
-      </c>
-      <c r="B22" s="7" t="inlineStr">
-        <is>
-          <t>Crédit conso limite basse montant</t>
-        </is>
-      </c>
-      <c r="C22" s="8" t="inlineStr">
-        <is>
-          <t>nominal</t>
-        </is>
-      </c>
-      <c r="D22" s="8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="E22" s="8" t="n">
-        <v>1200</v>
-      </c>
-      <c r="F22" s="8" t="inlineStr">
-        <is>
-          <t>ELIGIBLE</t>
+          <t>piege_endettement</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="n"/>
+      <c r="E15" s="8" t="n"/>
+      <c r="F15" s="8" t="n">
+        <v>180000</v>
+      </c>
+      <c r="G15" s="8" t="inlineStr">
+        <is>
+          <t>REFUSE</t>
         </is>
       </c>
     </row>
